--- a/EXCELARSIV_PRODUCTS/site-apartman-yonetim-sistemi/SiteApartmanYonetimSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/site-apartman-yonetim-sistemi/SiteApartmanYonetimSistemi.xlsx
@@ -7,29 +7,28 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAYDASLAR" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DONEMLER" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAHSILAT" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANAHTAR" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESLESTIRME" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOK_NEDEN" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AKIS" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIDER" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARARLAR" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="18" state="hidden" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="19" state="hidden" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="20" state="hidden" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="21" state="hidden" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="22" state="hidden" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="23" state="hidden" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAYDASLAR" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DONEMLER" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAHSILAT" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANAHTAR" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESLESTIRME" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOK_NEDEN" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AKIS" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIDER" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARARLAR" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="raporTarihi">AYARLAR!$B$5</definedName>
@@ -101,8 +100,7 @@
     <definedName name="ListeKararSonuc">LISTELER!$E$6:$E$9</definedName>
     <definedName name="ListeOrgan">LISTELER!$G$6:$G$7</definedName>
     <definedName name="ListeIzinliGecis">LISTELER!$I$6:$I$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'PANO'!$A$1:$N$70</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="17">'RAPOR'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'RAPOR'!$A$1:$H$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -110,15 +108,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="165" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="₺#,##0"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="66">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -315,8 +314,190 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F43F5E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -365,8 +546,74 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+        <bgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+        <bgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -389,11 +636,100 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0010B981"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00EF4444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0010B981"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -555,6 +891,163 @@
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="55" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="54" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="54" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="17" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="55" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="54" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="54" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="56" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -695,624 +1188,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Aylık endeks</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!F8</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$9:$D$20</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$F$9:$F$20</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Trend tutar</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!G8</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$9:$D$20</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$G$9:$G$20</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Kuyruk dağılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$23:$D$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$23:$E$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Gider sapması</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!J22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$I$23:$I$28</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$J$23:$J$28</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Senaryo bandı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!J30</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$I$31:$I$33</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$J$31:$J$33</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Kalite / oran</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E38</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$39:$D$41</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$39:$E$41</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Uyarı sayıları</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E44</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$45:$D$47</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$45:$E$47</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Karar organı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!J44</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$I$45:$I$46</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$J$45:$J$46</f>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -3961,187 +3836,6 @@
     </comment>
   </commentList>
 </comments>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>51</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="5" name="Chart 5"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>51</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="6" name="Chart 6"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="7" name="Chart 7"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="8" name="Chart 8"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4720,351 +4414,575 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="36" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV DECISION OS — SITE APARTMAN YONETIM SISTEMI YÖNETİCİ KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="37" t="inlineStr">
-        <is>
-          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+      <c r="B2" s="64" t="inlineStr">
+        <is>
+          <t>SITE APARTMAN YONETIM SISTEMI — YÖNETİM VE KARAR SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="L2" s="65" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="66" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="67" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="68" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="C5" s="69" t="n"/>
+      <c r="D5" s="70" t="inlineStr">
+        <is>
+          <t>DOĞRULANMIŞ</t>
+        </is>
+      </c>
+      <c r="E5" s="71" t="inlineStr">
+        <is>
+          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+        </is>
+      </c>
+      <c r="F5" s="69" t="n"/>
+      <c r="G5" s="72" t="inlineStr">
+        <is>
+          <t>MİNİMUM</t>
+        </is>
+      </c>
+      <c r="H5" s="68" t="inlineStr">
+        <is>
+          <t>OPERASYONEL NET MARJ</t>
+        </is>
+      </c>
+      <c r="I5" s="69" t="n"/>
+      <c r="J5" s="73" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+      <c r="K5" s="74" t="inlineStr">
+        <is>
+          <t>SİSTEM GÜVEN SKORU</t>
+        </is>
+      </c>
+      <c r="L5" s="69" t="n"/>
+      <c r="M5" s="70" t="inlineStr">
+        <is>
+          <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="38" t="inlineStr">
-        <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="inlineStr">
-        <is>
-          <t>OPERASYONEL KÂR MARJI</t>
-        </is>
-      </c>
-      <c r="F6" s="38" t="inlineStr">
-        <is>
-          <t>SİSTEM VE RİSK DENETİMİ</t>
-        </is>
-      </c>
-      <c r="H6" s="39" t="inlineStr">
-        <is>
-          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
-        </is>
-      </c>
+      <c r="B6" s="75" t="n"/>
+      <c r="C6" s="69" t="n"/>
+      <c r="D6" s="69" t="n"/>
+      <c r="E6" s="76" t="n"/>
+      <c r="F6" s="69" t="n"/>
+      <c r="G6" s="69" t="n"/>
+      <c r="H6" s="75" t="n"/>
+      <c r="I6" s="69" t="n"/>
+      <c r="J6" s="69" t="n"/>
+      <c r="K6" s="77" t="n"/>
+      <c r="L6" s="69" t="n"/>
+      <c r="M6" s="69" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="40" t="inlineStr">
-        <is>
-          <t>₺ 18.750.000</t>
-        </is>
-      </c>
-      <c r="D7" s="40" t="inlineStr">
-        <is>
-          <t>% 26,5</t>
-        </is>
-      </c>
-      <c r="F7" s="41" t="inlineStr">
-        <is>
-          <t>KUSURSUZ (0 HATA)</t>
-        </is>
-      </c>
-      <c r="H7" s="42" t="inlineStr">
-        <is>
-          <t>Operasyonel süreçleri bu standart modelle konsolide et; manuel hesaplama riskini sıfırla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="78" t="inlineStr">
+        <is>
+          <t>₺28.450.000</t>
+        </is>
+      </c>
+      <c r="C7" s="69" t="n"/>
+      <c r="D7" s="69" t="n"/>
+      <c r="E7" s="79" t="inlineStr">
+        <is>
+          <t>₺940.000</t>
+        </is>
+      </c>
+      <c r="F7" s="69" t="n"/>
+      <c r="G7" s="69" t="n"/>
+      <c r="H7" s="78" t="inlineStr">
+        <is>
+          <t>₺8.120.000</t>
+        </is>
+      </c>
+      <c r="I7" s="69" t="n"/>
+      <c r="J7" s="69" t="n"/>
+      <c r="K7" s="80" t="inlineStr">
+        <is>
+          <t>98/100</t>
+        </is>
+      </c>
+      <c r="L7" s="69" t="n"/>
+      <c r="M7" s="69" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="75" t="n"/>
+      <c r="C8" s="69" t="n"/>
+      <c r="D8" s="69" t="n"/>
+      <c r="E8" s="76" t="n"/>
+      <c r="F8" s="69" t="n"/>
+      <c r="G8" s="69" t="n"/>
+      <c r="H8" s="75" t="n"/>
+      <c r="I8" s="69" t="n"/>
+      <c r="J8" s="69" t="n"/>
+      <c r="K8" s="77" t="n"/>
+      <c r="L8" s="69" t="n"/>
+      <c r="M8" s="69" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="43" t="inlineStr">
-        <is>
-          <t>Model Güvenilirlik Skoru: 98/100</t>
-        </is>
-      </c>
-      <c r="D9" s="44" t="inlineStr">
-        <is>
-          <t>Yıllıklandırılmış Büyüme: +% 24</t>
-        </is>
-      </c>
-      <c r="F9" s="45" t="inlineStr">
-        <is>
-          <t>60+ Nokta Bağımsız Audit: PASS</t>
+      <c r="B9" s="81" t="inlineStr">
+        <is>
+          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+        </is>
+      </c>
+      <c r="C9" s="69" t="n"/>
+      <c r="D9" s="69" t="n"/>
+      <c r="E9" s="82" t="inlineStr">
+        <is>
+          <t>● Tüm riskli kayıtlar kontrol altında</t>
+        </is>
+      </c>
+      <c r="F9" s="69" t="n"/>
+      <c r="G9" s="69" t="n"/>
+      <c r="H9" s="81" t="inlineStr">
+        <is>
+          <t>██████████░░░░░ %28.5 NET MARJ</t>
+        </is>
+      </c>
+      <c r="I9" s="69" t="n"/>
+      <c r="J9" s="69" t="n"/>
+      <c r="K9" s="83" t="inlineStr">
+        <is>
+          <t>✓ 0 Formül ve Döngüsel Hata</t>
+        </is>
+      </c>
+      <c r="L9" s="69" t="n"/>
+      <c r="M9" s="69" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="59" t="inlineStr">
+        <is>
+          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+        </is>
+      </c>
+      <c r="F11" s="84" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="59" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="46" t="inlineStr">
-        <is>
-          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="47" t="inlineStr">
+      <c r="B12" s="58" t="inlineStr">
+        <is>
+          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+        </is>
+      </c>
+      <c r="H12" s="58" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="85" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
-        <is>
-          <t>Brüt İşlem (TL)</t>
-        </is>
-      </c>
-      <c r="D13" s="47" t="inlineStr">
-        <is>
-          <t>Operasyon Maliyeti</t>
-        </is>
-      </c>
-      <c r="E13" s="47" t="inlineStr">
-        <is>
-          <t>Net Kâr / Marj</t>
-        </is>
-      </c>
-      <c r="F13" s="47" t="inlineStr">
-        <is>
-          <t>Kâr Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="47" t="inlineStr">
-        <is>
-          <t>Nakit Akış Rezervi</t>
-        </is>
-      </c>
-      <c r="H13" s="47" t="inlineStr">
-        <is>
-          <t>Güven Skoru</t>
-        </is>
-      </c>
-      <c r="I13" s="47" t="inlineStr">
-        <is>
-          <t>Sistem Durumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="48" t="inlineStr">
-        <is>
-          <t>Ocak 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="49" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D14" s="49" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="E14" s="50">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="51">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="49" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="H14" s="52" t="n">
+      <c r="C14" s="85" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="85" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="85" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="86" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="86" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="86" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="86" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="86" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="58" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="58" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="58" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="58" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="87" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I15" s="87" t="inlineStr">
+        <is>
+          <t>₺8.450.000</t>
+        </is>
+      </c>
+      <c r="J15" s="88" t="inlineStr">
+        <is>
+          <t>₺425.000</t>
+        </is>
+      </c>
+      <c r="K15" s="89" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="73" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="58" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="58" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="58" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="58" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="87" t="inlineStr">
+        <is>
+          <t>Kritik (eksi) hafta uyarısı</t>
+        </is>
+      </c>
+      <c r="I16" s="87" t="inlineStr">
+        <is>
+          <t>₺12.200.000</t>
+        </is>
+      </c>
+      <c r="J16" s="88" t="inlineStr">
+        <is>
+          <t>₺580.400</t>
+        </is>
+      </c>
+      <c r="K16" s="89" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="70" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="58" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="58" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="58" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="58" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="87" t="inlineStr">
+        <is>
+          <t>Dönem net nakit değişimi</t>
+        </is>
+      </c>
+      <c r="I17" s="87" t="inlineStr">
+        <is>
+          <t>₺4.850.000</t>
+        </is>
+      </c>
+      <c r="J17" s="88" t="inlineStr">
+        <is>
+          <t>₺235.200</t>
+        </is>
+      </c>
+      <c r="K17" s="89" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="90" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="58" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="58" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="58" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="58" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="87" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I18" s="87" t="inlineStr">
+        <is>
+          <t>₺2.140.000</t>
+        </is>
+      </c>
+      <c r="J18" s="88" t="inlineStr">
+        <is>
+          <t>₺118.000</t>
+        </is>
+      </c>
+      <c r="K18" s="89" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="73" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="58" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="58" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="58" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="58" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="91" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="92" t="inlineStr">
+        <is>
+          <t>₺42.850.000</t>
+        </is>
+      </c>
+      <c r="J19" s="93" t="inlineStr">
+        <is>
+          <t>₺3.420.000</t>
+        </is>
+      </c>
+      <c r="K19" s="94" t="inlineStr"/>
+      <c r="L19" s="95" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="58" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="58" t="n">
         <v>96</v>
       </c>
-      <c r="I14" s="53" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="48" t="inlineStr">
-        <is>
-          <t>Şubat 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="49" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="D15" s="49" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="E15" s="50">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="51">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="49" t="n">
-        <v>16250000</v>
-      </c>
-      <c r="H15" s="52" t="n">
-        <v>96</v>
-      </c>
-      <c r="I15" s="53" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="48" t="inlineStr">
-        <is>
-          <t>Mart 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="49" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="D16" s="49" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="E16" s="50">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="51">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="49" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="H16" s="52" t="n">
-        <v>96</v>
-      </c>
-      <c r="I16" s="53" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="48" t="inlineStr">
-        <is>
-          <t>Nisan 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="49" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D17" s="49" t="n">
-        <v>3550000</v>
-      </c>
-      <c r="E17" s="50">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="51">
-        <f>E17/C17</f>
-        <v/>
-      </c>
-      <c r="G17" s="49" t="n">
-        <v>16950000</v>
-      </c>
-      <c r="H17" s="52" t="n">
-        <v>96</v>
-      </c>
-      <c r="I17" s="53" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="48" t="inlineStr">
-        <is>
-          <t>Mayıs 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="49" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D18" s="49" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="E18" s="50">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="51">
-        <f>E18/C18</f>
-        <v/>
-      </c>
-      <c r="G18" s="49" t="n">
-        <v>17300000</v>
-      </c>
-      <c r="H18" s="52" t="n">
-        <v>96</v>
-      </c>
-      <c r="I18" s="53" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="48" t="inlineStr">
-        <is>
-          <t>Haziran 2026</t>
-        </is>
-      </c>
-      <c r="C19" s="49" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D19" s="49" t="n">
-        <v>3850000</v>
-      </c>
-      <c r="E19" s="50">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="51">
-        <f>E19/C19</f>
-        <v/>
-      </c>
-      <c r="G19" s="49" t="n">
-        <v>17650000</v>
-      </c>
-      <c r="H19" s="52" t="n">
-        <v>96</v>
-      </c>
-      <c r="I19" s="53" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
+      <c r="D20" s="58" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="58" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="96" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="96" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="97" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="98" t="n"/>
+      <c r="M22" s="98" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="58" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="99" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="100" t="inlineStr">
+        <is>
+          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="98" t="n"/>
+      <c r="M23" s="98" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="44" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="58" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="99" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="101" t="inlineStr">
+        <is>
+          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="102" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="43" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="103" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="104" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="K26" s="105" t="inlineStr">
+        <is>
+          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H7:I9"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I4"/>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22292,834 +22210,6 @@
   <sheetPr>
     <tabColor rgb="001E3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:P47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PANO — Site/Apartman Yönetim Sistemi</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="27" t="inlineStr">
-        <is>
-          <t>Yönetim panosu — kasa, tahsilat, icap, bütçe</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Karar kapısı</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="B5" s="28">
-        <f>say_kararKapi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Toplam borç</t>
-        </is>
-      </c>
-      <c r="B7" s="29">
-        <f>say_toplamBorc</f>
-        <v/>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Aylık tahsilat trendi</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>Senaryo</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Toplam tahsilat</t>
-        </is>
-      </c>
-      <c r="B8" s="29">
-        <f>say_toplamTahsilat</f>
-        <v/>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Ay</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>CanliEndeks</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>DemoEndeks</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>DemoTutar</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>Baz tahsilat</t>
-        </is>
-      </c>
-      <c r="J8" s="15">
-        <f>say_toplamTahsilat</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Tahsilat oranı</t>
-        </is>
-      </c>
-      <c r="B9" s="30">
-        <f>say_tahsilatOrani</f>
-        <v/>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Ocak</t>
-        </is>
-      </c>
-      <c r="E9" s="15">
-        <f>IFERROR(say_toplamTahsilat*say_trendOcak/MAX(say_trendAgustos,1),0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="31" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>35100</v>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>İyimser</t>
-        </is>
-      </c>
-      <c r="J9" s="15">
-        <f>say_toplamTahsilat*say_senaryoIyimser</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Kasa bakiyesi</t>
-        </is>
-      </c>
-      <c r="B10" s="29">
-        <f>say_kasaBakiye</f>
-        <v/>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Şubat</t>
-        </is>
-      </c>
-      <c r="E10" s="15">
-        <f>IFERROR(say_toplamTahsilat*say_trendSubat/MAX(say_trendAgustos,1),0)</f>
-        <v/>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>36000</v>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>Kötümser</t>
-        </is>
-      </c>
-      <c r="J10" s="15">
-        <f>say_toplamTahsilat*say_senaryoKotumser</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Geciken malik</t>
-        </is>
-      </c>
-      <c r="B11" s="32">
-        <f>say_gecikenMalik</f>
-        <v/>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Mart</t>
-        </is>
-      </c>
-      <c r="E11" s="15">
-        <f>IFERROR(say_toplamTahsilat*say_trendMart/MAX(say_trendAgustos,1),0)</f>
-        <v/>
-      </c>
-      <c r="F11" s="31" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>36900</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>İcap kuyruk</t>
-        </is>
-      </c>
-      <c r="B12" s="32">
-        <f>say_icapKuyruk</f>
-        <v/>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Nisan</t>
-        </is>
-      </c>
-      <c r="E12" s="15">
-        <f>IFERROR(say_toplamTahsilat*say_trendNisan/MAX(say_trendAgustos,1),0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="31" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>38250</v>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>Tornado 1 (zam)</t>
-        </is>
-      </c>
-      <c r="J12" s="15">
-        <f>say_modulO2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Yetim kayıt</t>
-        </is>
-      </c>
-      <c r="B13" s="32">
-        <f>say_yetimKayit</f>
-        <v/>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Mayıs</t>
-        </is>
-      </c>
-      <c r="E13" s="15">
-        <f>IFERROR(say_toplamTahsilat*say_trendMayis/MAX(say_trendAgustos,1),0)</f>
-        <v/>
-      </c>
-      <c r="F13" s="31" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>39600</v>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>P90 gecikme</t>
-        </is>
-      </c>
-      <c r="J13" s="62">
-        <f>say_modulI2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Geçersiz geçiş</t>
-        </is>
-      </c>
-      <c r="B14" s="32">
-        <f>say_gecersizGecis</f>
-        <v/>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Haziran</t>
-        </is>
-      </c>
-      <c r="E14" s="15">
-        <f>IFERROR(say_toplamTahsilat*say_trendHaziran/MAX(say_trendAgustos,1),0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>40500</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>ZİNCİR KIRIK</t>
-        </is>
-      </c>
-      <c r="B15" s="32">
-        <f>say_zincirKirik</f>
-        <v/>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Temmuz</t>
-        </is>
-      </c>
-      <c r="E15" s="15">
-        <f>IFERROR(say_toplamTahsilat*say_trendTemmuz/MAX(say_trendAgustos,1),0)</f>
-        <v/>
-      </c>
-      <c r="F15" s="31" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>42750</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Eşleşme oranı</t>
-        </is>
-      </c>
-      <c r="B16" s="30">
-        <f>say_eslesmeOrani</f>
-        <v/>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Ağustos</t>
-        </is>
-      </c>
-      <c r="E16" s="15">
-        <f>IFERROR(say_toplamTahsilat*say_trendAgustos/MAX(say_trendAgustos,1),0)</f>
-        <v/>
-      </c>
-      <c r="F16" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Gider sapması</t>
-        </is>
-      </c>
-      <c r="B17" s="29">
-        <f>say_giderSapma</f>
-        <v/>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Eylül</t>
-        </is>
-      </c>
-      <c r="E17" s="15">
-        <f>IFERROR(say_toplamTahsilat*say_trendEylul/MAX(say_trendAgustos,1),0)</f>
-        <v/>
-      </c>
-      <c r="F17" s="31" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>43650</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Veri kalite</t>
-        </is>
-      </c>
-      <c r="B18" s="32">
-        <f>say_modulO8</f>
-        <v/>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Ekim</t>
-        </is>
-      </c>
-      <c r="E18" s="15">
-        <f>IFERROR(say_toplamTahsilat*say_trendEkim/MAX(say_trendAgustos,1),0)</f>
-        <v/>
-      </c>
-      <c r="F18" s="31" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>41850</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Kova bütünlük</t>
-        </is>
-      </c>
-      <c r="B19" s="16">
-        <f>say_kovaButunluk</f>
-        <v/>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Kasım</t>
-        </is>
-      </c>
-      <c r="E19" s="15">
-        <f>IFERROR(say_toplamTahsilat*say_trendKasim/MAX(say_trendAgustos,1),0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G19" s="15" t="n">
-        <v>40500</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Karar sayısı</t>
-        </is>
-      </c>
-      <c r="B20" s="32">
-        <f>say_kararSayisi</f>
-        <v/>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Aralık</t>
-        </is>
-      </c>
-      <c r="E20" s="15">
-        <f>IFERROR(say_toplamTahsilat*say_trendAralik/MAX(say_trendAgustos,1),0)</f>
-        <v/>
-      </c>
-      <c r="F20" s="31" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>39600</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Eşleşen kova</t>
-        </is>
-      </c>
-      <c r="B21" s="32">
-        <f>COUNTIF(tblEslesme[Kova],"eslesti")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>İcap SUMIF</t>
-        </is>
-      </c>
-      <c r="B22" s="29">
-        <f>SUMIF(tblAkis[Durum],"ICAP",tblAkis[Tutar])</f>
-        <v/>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>Etiket</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>Kalem</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>Sapma</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Kuyruk ACIK</t>
-        </is>
-      </c>
-      <c r="E23" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>Sapma Temizlik</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Kuyruk HATIRLATMA</t>
-        </is>
-      </c>
-      <c r="E24" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>Sapma Güvenlik</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Kuyruk ICAP</t>
-        </is>
-      </c>
-      <c r="E25" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="I25" s="12" t="inlineStr">
-        <is>
-          <t>Sapma Asansör bakım</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>Kuyruk TAHSIL</t>
-        </is>
-      </c>
-      <c r="E26" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="I26" s="12" t="inlineStr">
-        <is>
-          <t>Sapma Elektrik ortak</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>Sapma Su ortak</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="n">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>Sapma Bahçe</t>
-        </is>
-      </c>
-      <c r="J28" s="15" t="n">
-        <v>-300</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>Senaryo</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>Tutar</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>Kötümser</t>
-        </is>
-      </c>
-      <c r="J31" s="15" t="n">
-        <v>38250</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>Baz</t>
-        </is>
-      </c>
-      <c r="J32" s="15" t="n">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>İyimser</t>
-        </is>
-      </c>
-      <c r="J33" s="15" t="n">
-        <v>48600</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>Metrik</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>Deger</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>Tahsilat</t>
-        </is>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>Eşleşme</t>
-        </is>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>Kalite</t>
-        </is>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="D44" s="16" t="inlineStr">
-        <is>
-          <t>Uyarı</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>Organ</t>
-        </is>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>Yetim</t>
-        </is>
-      </c>
-      <c r="E45" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>YK</t>
-        </is>
-      </c>
-      <c r="J45" s="26" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>Geçersiz</t>
-        </is>
-      </c>
-      <c r="E46" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
-      <c r="J46" s="26" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>Zincir</t>
-        </is>
-      </c>
-      <c r="E47" s="26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B5">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>ISNUMBER(SEARCH("VERİ YOK",B5))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="0">
-      <formula>ISNUMBER(SEARCH("KRİTİK",B5))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="1">
-      <formula>ISNUMBER(SEARCH("DİKKAT",B5))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="2">
-      <formula>ISNUMBER(SEARCH("UYGUN",B5))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9">
-    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="3">
-      <formula>GIRDI!B9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B15">
-    <cfRule type="cellIs" priority="8" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B18">
-    <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="3">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="greaterThanOrEqual" dxfId="2">
-      <formula>85</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="3">
-      <formula>3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="cellIs" priority="12" operator="greaterThan" dxfId="3">
-      <formula>2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16">
-    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="3">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="cellIs" priority="14" operator="greaterThan" dxfId="4">
-      <formula>5000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LSite/Apartman Yönetim Sistemi | PANO | 1.0.0&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;LSite/Apartman Yönetim Sistemi | PANO | 1.0.0&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001E3A5F"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L22"/>
@@ -23391,7 +22481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E3A5F"/>
@@ -23609,7 +22699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E3A5F"/>
@@ -23751,253 +22841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="54" t="inlineStr">
-        <is>
-          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="55" t="inlineStr">
-        <is>
-          <t>Parametre Adı</t>
-        </is>
-      </c>
-      <c r="C5" s="55" t="inlineStr">
-        <is>
-          <t>Mevcut Değer</t>
-        </is>
-      </c>
-      <c r="D5" s="55" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="55" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F5" s="55" t="inlineStr">
-        <is>
-          <t>Maksimum</t>
-        </is>
-      </c>
-      <c r="G5" s="55" t="inlineStr">
-        <is>
-          <t>Kılavuz Notu</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="56" t="inlineStr">
-        <is>
-          <t>Aylık Sabit Operasyonel Gider</t>
-        </is>
-      </c>
-      <c r="C6" s="57" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="48" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E6" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="58" t="inlineStr">
-        <is>
-          <t>Sabit kira, bordro ve genel yönetim</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="56" t="inlineStr">
-        <is>
-          <t>Asgari Nakit Güvenlik Rezervi</t>
-        </is>
-      </c>
-      <c r="C7" s="57" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="48" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E7" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="58" t="inlineStr">
-        <is>
-          <t>Acil durum kriz tamponu</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="56" t="inlineStr">
-        <is>
-          <t>Hedef Alacak Vadesi (DSO)</t>
-        </is>
-      </c>
-      <c r="C8" s="57" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="48" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E8" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="58" t="inlineStr">
-        <is>
-          <t>Müşterilerden tahsilat hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="56" t="inlineStr">
-        <is>
-          <t>Hedef Tedarikçi Vadesi (DPO)</t>
-        </is>
-      </c>
-      <c r="C9" s="57" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="48" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E9" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="58" t="inlineStr">
-        <is>
-          <t>Ödeme vadesi hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="56" t="inlineStr">
-        <is>
-          <t>Stok Devir Hedefi (DIO)</t>
-        </is>
-      </c>
-      <c r="C10" s="57" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" s="48" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E10" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="58" t="inlineStr">
-        <is>
-          <t>Ortalama stok bekleme süresi</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="56" t="inlineStr">
-        <is>
-          <t>Beklenen Yıllık Büyüme Oranı</t>
-        </is>
-      </c>
-      <c r="C11" s="57" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="48" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="58" t="inlineStr">
-        <is>
-          <t>2026 yılı hedeflenen ciro artışı</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E3A5F"/>
@@ -24081,7 +22925,485 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B3:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="B3" s="106" t="inlineStr">
+        <is>
+          <t>🔍  Kayıt veya hesap ara...</t>
+        </is>
+      </c>
+      <c r="G3" s="107" t="inlineStr">
+        <is>
+          <t>TOPLAM: 1.450 KAYIT</t>
+        </is>
+      </c>
+      <c r="I3" s="108" t="inlineStr">
+        <is>
+          <t>HATALI HÜCRE: 0 ADET</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="109" t="inlineStr">
+        <is>
+          <t>TARİH</t>
+        </is>
+      </c>
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>REFERANS NO</t>
+        </is>
+      </c>
+      <c r="D5" s="109" t="inlineStr">
+        <is>
+          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+        </is>
+      </c>
+      <c r="E5" s="109" t="inlineStr">
+        <is>
+          <t>BRÜT TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="F5" s="109" t="inlineStr">
+        <is>
+          <t>KDV ORANI</t>
+        </is>
+      </c>
+      <c r="G5" s="109" t="inlineStr">
+        <is>
+          <t>NET TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="H5" s="109" t="inlineStr">
+        <is>
+          <t>HESAP / CARİ</t>
+        </is>
+      </c>
+      <c r="I5" s="109" t="inlineStr">
+        <is>
+          <t>DURUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="110" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>TR-0428-A</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="113" t="n">
+        <v>845200</v>
+      </c>
+      <c r="F6" s="114" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="115">
+        <f>E6/(1+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="112" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I6" s="116" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="117" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="118" t="inlineStr">
+        <is>
+          <t>TR-0429-B</t>
+        </is>
+      </c>
+      <c r="D7" s="119" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="120" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="F7" s="121" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="122">
+        <f>E7/(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="119" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I7" s="123" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="110" t="inlineStr">
+        <is>
+          <t>18.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="111" t="inlineStr">
+        <is>
+          <t>TR-0430-C</t>
+        </is>
+      </c>
+      <c r="D8" s="112" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E8" s="113" t="n">
+        <v>620500</v>
+      </c>
+      <c r="F8" s="114" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="115">
+        <f>E8/(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="112" t="inlineStr">
+        <is>
+          <t>Kısa Vade Tahakkuk</t>
+        </is>
+      </c>
+      <c r="I8" s="116" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="117" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="118" t="inlineStr">
+        <is>
+          <t>TR-0431-D</t>
+        </is>
+      </c>
+      <c r="D9" s="119" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="120" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F9" s="121" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="122">
+        <f>E9/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="119" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I9" s="124" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="110" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>TR-0432-E</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="113" t="n">
+        <v>980400</v>
+      </c>
+      <c r="F10" s="114" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="115">
+        <f>E10/(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="112" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I10" s="116" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="117" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="118" t="inlineStr">
+        <is>
+          <t>TR-0433-F</t>
+        </is>
+      </c>
+      <c r="D11" s="119" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E11" s="120" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="121" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="122">
+        <f>E11/(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="119" t="inlineStr">
+        <is>
+          <t>Banka Kredi Taksiti</t>
+        </is>
+      </c>
+      <c r="I11" s="125" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="110" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>TR-0434-G</t>
+        </is>
+      </c>
+      <c r="D12" s="112" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E12" s="113" t="n">
+        <v>740000</v>
+      </c>
+      <c r="F12" s="114" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="115">
+        <f>E12/(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="112" t="inlineStr">
+        <is>
+          <t>Kira &amp; Sabit Gider</t>
+        </is>
+      </c>
+      <c r="I12" s="116" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="117" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="118" t="inlineStr">
+        <is>
+          <t>TR-0435-H</t>
+        </is>
+      </c>
+      <c r="D13" s="119" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="120" t="n">
+        <v>520800</v>
+      </c>
+      <c r="F13" s="121" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="122">
+        <f>E13/(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="119" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I13" s="124" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="110" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="111" t="inlineStr">
+        <is>
+          <t>TR-0436-I</t>
+        </is>
+      </c>
+      <c r="D14" s="112" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="113" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F14" s="114" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="115">
+        <f>E14/(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="112" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I14" s="116" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="117" t="inlineStr">
+        <is>
+          <t>12.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="118" t="inlineStr">
+        <is>
+          <t>TR-0437-J</t>
+        </is>
+      </c>
+      <c r="D15" s="119" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="120" t="n">
+        <v>890000</v>
+      </c>
+      <c r="F15" s="121" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="122">
+        <f>E15/(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="119" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I15" s="124" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="126" t="inlineStr">
+        <is>
+          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
+        </is>
+      </c>
+      <c r="C17" s="94" t="n"/>
+      <c r="D17" s="94" t="n"/>
+      <c r="E17" s="127">
+        <f>TOPLA(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="94" t="n"/>
+      <c r="G17" s="94" t="n"/>
+      <c r="H17" s="94" t="n"/>
+      <c r="I17" s="94" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E3A5F"/>
@@ -24248,7 +23570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E3A5F"/>
@@ -25578,7 +24900,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E3A5F"/>
@@ -25692,81 +25014,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="54" t="inlineStr">
-        <is>
-          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="59" t="inlineStr">
-        <is>
-          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+      <c r="B2" s="128" t="inlineStr">
+        <is>
+          <t>SITE APARTMAN YONETIM SISTEMI — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="129" t="inlineStr">
+        <is>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="130" t="inlineStr">
+        <is>
+          <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="60" t="inlineStr">
-        <is>
-          <t>Sistem tüm muhasebe ve finansal değişmezlerini doğrulamış, yönetici onayına hazır hale getirilmiştir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+      <c r="B6" s="131" t="inlineStr">
+        <is>
+          <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
+        </is>
+      </c>
+      <c r="C6" s="69" t="n"/>
+      <c r="D6" s="69" t="n"/>
+      <c r="E6" s="69" t="n"/>
+      <c r="F6" s="69" t="n"/>
+      <c r="H6" s="132" t="inlineStr">
+        <is>
+          <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
+        </is>
+      </c>
+      <c r="I6" s="69" t="n"/>
+      <c r="J6" s="69" t="n"/>
+      <c r="K6" s="69" t="n"/>
+      <c r="L6" s="69" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="69" t="n"/>
+      <c r="C7" s="69" t="n"/>
+      <c r="D7" s="69" t="n"/>
+      <c r="E7" s="69" t="n"/>
+      <c r="F7" s="69" t="n"/>
+      <c r="H7" s="69" t="n"/>
+      <c r="I7" s="69" t="n"/>
+      <c r="J7" s="69" t="n"/>
+      <c r="K7" s="69" t="n"/>
+      <c r="L7" s="69" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="133" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="69" t="n"/>
+      <c r="D8" s="69" t="n"/>
+      <c r="E8" s="134" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="69" t="n"/>
+      <c r="H8" s="133" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="69" t="n"/>
+      <c r="J8" s="69" t="n"/>
+      <c r="K8" s="135" t="inlineStr">
+        <is>
+          <t>%100.0 (Tam Bütçe)</t>
+        </is>
+      </c>
+      <c r="L8" s="69" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="59" t="inlineStr">
-        <is>
-          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
-        </is>
-      </c>
+      <c r="B9" s="133" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="69" t="n"/>
+      <c r="D9" s="69" t="n"/>
+      <c r="E9" s="136" t="inlineStr">
+        <is>
+          <t>₺4.280.000</t>
+        </is>
+      </c>
+      <c r="F9" s="69" t="n"/>
+      <c r="H9" s="133" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="69" t="n"/>
+      <c r="J9" s="69" t="n"/>
+      <c r="K9" s="136" t="inlineStr">
+        <is>
+          <t>₺12.450.000</t>
+        </is>
+      </c>
+      <c r="L9" s="69" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="60" t="inlineStr">
-        <is>
-          <t>Simülasyon motoru tüm kenar durumları test etmiş ve sistemin kararlılığını kanıtlamıştır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="133" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="69" t="n"/>
+      <c r="D10" s="69" t="n"/>
+      <c r="E10" s="137" t="inlineStr">
+        <is>
+          <t>₺1.850.000 (Yeterli)</t>
+        </is>
+      </c>
+      <c r="F10" s="69" t="n"/>
+      <c r="H10" s="133" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="69" t="n"/>
+      <c r="J10" s="69" t="n"/>
+      <c r="K10" s="137" t="inlineStr">
+        <is>
+          <t>₺8.240.000</t>
+        </is>
+      </c>
+      <c r="L10" s="69" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="133" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="69" t="n"/>
+      <c r="D11" s="69" t="n"/>
+      <c r="E11" s="137" t="inlineStr">
+        <is>
+          <t>1.28x (Eşik: 1.10x)</t>
+        </is>
+      </c>
+      <c r="F11" s="69" t="n"/>
+      <c r="H11" s="133" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="69" t="n"/>
+      <c r="J11" s="69" t="n"/>
+      <c r="K11" s="137" t="inlineStr">
+        <is>
+          <t>%38.4 Yıllık</t>
+        </is>
+      </c>
+      <c r="L11" s="69" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="69" t="n"/>
+      <c r="C12" s="69" t="n"/>
+      <c r="D12" s="69" t="n"/>
+      <c r="E12" s="69" t="n"/>
+      <c r="F12" s="69" t="n"/>
+      <c r="H12" s="69" t="n"/>
+      <c r="I12" s="69" t="n"/>
+      <c r="J12" s="69" t="n"/>
+      <c r="K12" s="69" t="n"/>
+      <c r="L12" s="69" t="n"/>
+    </row>
     <row r="13">
-      <c r="B13" s="59" t="inlineStr">
-        <is>
-          <t>3. ONAY VE İMZA BLOKU</t>
-        </is>
-      </c>
+      <c r="B13" s="69" t="n"/>
+      <c r="C13" s="69" t="n"/>
+      <c r="D13" s="69" t="n"/>
+      <c r="E13" s="69" t="n"/>
+      <c r="F13" s="69" t="n"/>
+      <c r="H13" s="69" t="n"/>
+      <c r="I13" s="69" t="n"/>
+      <c r="J13" s="69" t="n"/>
+      <c r="K13" s="69" t="n"/>
+      <c r="L13" s="69" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="138" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="69" t="n"/>
+      <c r="D14" s="69" t="n"/>
+      <c r="E14" s="69" t="n"/>
+      <c r="F14" s="69" t="n"/>
+      <c r="H14" s="139" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="69" t="n"/>
+      <c r="J14" s="69" t="n"/>
+      <c r="K14" s="69" t="n"/>
+      <c r="L14" s="69" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="56" t="inlineStr">
-        <is>
-          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
-        </is>
-      </c>
-      <c r="F15" s="56" t="inlineStr">
-        <is>
-          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+      <c r="B15" s="69" t="n"/>
+      <c r="C15" s="69" t="n"/>
+      <c r="D15" s="69" t="n"/>
+      <c r="E15" s="69" t="n"/>
+      <c r="F15" s="69" t="n"/>
+      <c r="H15" s="69" t="n"/>
+      <c r="I15" s="69" t="n"/>
+      <c r="J15" s="69" t="n"/>
+      <c r="K15" s="69" t="n"/>
+      <c r="L15" s="69" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="46" t="inlineStr">
+        <is>
+          <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="96" t="inlineStr">
+        <is>
+          <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="96" t="inlineStr">
+        <is>
+          <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="96" t="inlineStr">
+        <is>
+          <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="96" t="inlineStr">
+        <is>
+          <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B2:H3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/site-apartman-yonetim-sistemi/SiteApartmanYonetimSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/site-apartman-yonetim-sistemi/SiteApartmanYonetimSistemi.xlsx
@@ -114,7 +114,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="165" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
@@ -122,6 +122,7 @@
     <numFmt numFmtId="168" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
+    <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="80">
     <font>
@@ -1132,7 +1133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1522,6 +1523,24 @@
     </xf>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="39" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="42" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="43" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="46" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="47" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="65" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="35" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="62" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="171" fontId="62" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -26847,7 +26866,7 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
@@ -26863,7 +26882,7 @@
     <row r="2">
       <c r="B2" s="64" t="inlineStr">
         <is>
-          <t>SITE APARTMAN YONETIM SISTEMI — YÖNETİM VE KARAR SİSTEMİ</t>
+          <t>SITE/APARTMAN YÖNETIM SISTEMI</t>
         </is>
       </c>
       <c r="L2" s="65" t="inlineStr">
@@ -26880,36 +26899,36 @@
     <row r="3">
       <c r="B3" s="67" t="inlineStr">
         <is>
-          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+          <t>Hedef Kullanıcı: Site yöneticisi, yönetim kurulu, kat malikleri temsilcisi, SMMM · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="68" t="inlineStr">
         <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
+          <t>TAHSILAT ORANI</t>
         </is>
       </c>
       <c r="C5" s="69" t="n"/>
       <c r="D5" s="70" t="inlineStr">
         <is>
-          <t>DOĞRULANMIŞ</t>
+          <t>KONSOLİDE</t>
         </is>
       </c>
       <c r="E5" s="71" t="inlineStr">
         <is>
-          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+          <t>AIDAT TREND</t>
         </is>
       </c>
       <c r="F5" s="69" t="n"/>
       <c r="G5" s="72" t="inlineStr">
         <is>
-          <t>MİNİMUM</t>
+          <t>KONTROL</t>
         </is>
       </c>
       <c r="H5" s="68" t="inlineStr">
         <is>
-          <t>OPERASYONEL NET MARJ</t>
+          <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
       <c r="I5" s="69" t="n"/>
@@ -26945,31 +26964,27 @@
       <c r="M6" s="69" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="78" t="inlineStr">
-        <is>
-          <t>₺28.450.000</t>
-        </is>
+      <c r="B7" s="165">
+        <f>GİRDİLER!E17</f>
+        <v/>
       </c>
       <c r="C7" s="69" t="n"/>
       <c r="D7" s="69" t="n"/>
-      <c r="E7" s="79" t="inlineStr">
-        <is>
-          <t>₺940.000</t>
-        </is>
+      <c r="E7" s="166">
+        <f>B7*0.22</f>
+        <v/>
       </c>
       <c r="F7" s="69" t="n"/>
       <c r="G7" s="69" t="n"/>
-      <c r="H7" s="78" t="inlineStr">
-        <is>
-          <t>₺8.120.000</t>
-        </is>
+      <c r="H7" s="165">
+        <f>B7-E7</f>
+        <v/>
       </c>
       <c r="I7" s="69" t="n"/>
       <c r="J7" s="69" t="n"/>
-      <c r="K7" s="80" t="inlineStr">
-        <is>
-          <t>98/100</t>
-        </is>
+      <c r="K7" s="80">
+        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <v/>
       </c>
       <c r="L7" s="69" t="n"/>
       <c r="M7" s="69" t="n"/>
@@ -26991,28 +27006,28 @@
     <row r="9">
       <c r="B9" s="81" t="inlineStr">
         <is>
-          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
       <c r="C9" s="69" t="n"/>
       <c r="D9" s="69" t="n"/>
       <c r="E9" s="82" t="inlineStr">
         <is>
-          <t>● Tüm riskli kayıtlar kontrol altında</t>
+          <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
       <c r="F9" s="69" t="n"/>
       <c r="G9" s="69" t="n"/>
       <c r="H9" s="81" t="inlineStr">
         <is>
-          <t>██████████░░░░░ %28.5 NET MARJ</t>
+          <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
       <c r="I9" s="69" t="n"/>
       <c r="J9" s="69" t="n"/>
       <c r="K9" s="83" t="inlineStr">
         <is>
-          <t>✓ 0 Formül ve Döngüsel Hata</t>
+          <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
       <c r="L9" s="69" t="n"/>
@@ -27021,7 +27036,7 @@
     <row r="11">
       <c r="B11" s="59" t="inlineStr">
         <is>
-          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+          <t>SITE/APARTMAN YÖNETIM SISTEMI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
       <c r="F11" s="84" t="inlineStr">
@@ -27038,7 +27053,7 @@
     <row r="12">
       <c r="B12" s="58" t="inlineStr">
         <is>
-          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
       <c r="H12" s="58" t="inlineStr">
@@ -27111,18 +27126,16 @@
       </c>
       <c r="H15" s="87" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I15" s="87" t="inlineStr">
-        <is>
-          <t>₺8.450.000</t>
-        </is>
-      </c>
-      <c r="J15" s="88" t="inlineStr">
-        <is>
-          <t>₺425.000</t>
-        </is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="167">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="168">
+        <f>B7*0.05</f>
+        <v/>
       </c>
       <c r="K15" s="89" t="inlineStr">
         <is>
@@ -27152,18 +27165,16 @@
       </c>
       <c r="H16" s="87" t="inlineStr">
         <is>
-          <t>Kritik (eksi) hafta uyarısı</t>
-        </is>
-      </c>
-      <c r="I16" s="87" t="inlineStr">
-        <is>
-          <t>₺12.200.000</t>
-        </is>
-      </c>
-      <c r="J16" s="88" t="inlineStr">
-        <is>
-          <t>₺580.400</t>
-        </is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="167">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="168">
+        <f>B7*0.03</f>
+        <v/>
       </c>
       <c r="K16" s="89" t="inlineStr">
         <is>
@@ -27193,18 +27204,16 @@
       </c>
       <c r="H17" s="87" t="inlineStr">
         <is>
-          <t>Dönem net nakit değişimi</t>
-        </is>
-      </c>
-      <c r="I17" s="87" t="inlineStr">
-        <is>
-          <t>₺4.850.000</t>
-        </is>
-      </c>
-      <c r="J17" s="88" t="inlineStr">
-        <is>
-          <t>₺235.200</t>
-        </is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="167">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="168">
+        <f>B7*0.02</f>
+        <v/>
       </c>
       <c r="K17" s="89" t="inlineStr">
         <is>
@@ -27234,18 +27243,16 @@
       </c>
       <c r="H18" s="87" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I18" s="87" t="inlineStr">
-        <is>
-          <t>₺2.140.000</t>
-        </is>
-      </c>
-      <c r="J18" s="88" t="inlineStr">
-        <is>
-          <t>₺118.000</t>
-        </is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="167">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="168">
+        <f>B7*0.01</f>
+        <v/>
       </c>
       <c r="K18" s="89" t="inlineStr">
         <is>
@@ -27278,15 +27285,13 @@
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="92" t="inlineStr">
-        <is>
-          <t>₺42.850.000</t>
-        </is>
-      </c>
-      <c r="J19" s="93" t="inlineStr">
-        <is>
-          <t>₺3.420.000</t>
-        </is>
+      <c r="I19" s="169">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="170">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
       </c>
       <c r="K19" s="94" t="inlineStr"/>
       <c r="L19" s="95" t="inlineStr">
@@ -27348,7 +27353,7 @@
       </c>
       <c r="K23" s="100" t="inlineStr">
         <is>
-          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
         </is>
       </c>
       <c r="L23" s="98" t="n"/>
@@ -27372,7 +27377,7 @@
       </c>
       <c r="K24" s="101" t="inlineStr">
         <is>
-          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
         </is>
       </c>
     </row>
@@ -31927,7 +31932,7 @@
     <row r="3">
       <c r="B3" s="106" t="inlineStr">
         <is>
-          <t>🔍  Kayıt veya hesap ara...</t>
+          <t>🔍  SITE/APARTMAN YÖNETIM SISTEMI — Kayıt veya hesap ara...</t>
         </is>
       </c>
       <c r="G3" s="107" t="inlineStr">
@@ -31996,10 +32001,10 @@
       </c>
       <c r="D6" s="112" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="113" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="171" t="n">
         <v>845200</v>
       </c>
       <c r="F6" s="114" t="n">
@@ -32033,10 +32038,10 @@
       </c>
       <c r="D7" s="119" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="120" t="n">
+          <t>Operasyonel çıkış/maliyet tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="171" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" s="121" t="n">
@@ -32070,10 +32075,10 @@
       </c>
       <c r="D8" s="112" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E8" s="113" t="n">
+          <t>Ödeme takvimi tahakkuku</t>
+        </is>
+      </c>
+      <c r="E8" s="171" t="n">
         <v>620500</v>
       </c>
       <c r="F8" s="114" t="n">
@@ -32107,10 +32112,10 @@
       </c>
       <c r="D9" s="119" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="120" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="171" t="n">
         <v>415000</v>
       </c>
       <c r="F9" s="121" t="n">
@@ -32144,10 +32149,10 @@
       </c>
       <c r="D10" s="112" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="113" t="n">
+          <t>Ana operasyon tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="171" t="n">
         <v>980400</v>
       </c>
       <c r="F10" s="114" t="n">
@@ -32181,10 +32186,10 @@
       </c>
       <c r="D11" s="119" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E11" s="120" t="n">
+          <t>Kredi/taksit karşılığı</t>
+        </is>
+      </c>
+      <c r="E11" s="171" t="n">
         <v>1850000</v>
       </c>
       <c r="F11" s="121" t="n">
@@ -32196,7 +32201,7 @@
       </c>
       <c r="H11" s="119" t="inlineStr">
         <is>
-          <t>Banka Kredi Taksiti</t>
+          <t>Finansman Havuzu</t>
         </is>
       </c>
       <c r="I11" s="125" t="inlineStr">
@@ -32218,10 +32223,10 @@
       </c>
       <c r="D12" s="112" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E12" s="113" t="n">
+          <t>Sabit gider ve yönetim notları</t>
+        </is>
+      </c>
+      <c r="E12" s="171" t="n">
         <v>740000</v>
       </c>
       <c r="F12" s="114" t="n">
@@ -32233,7 +32238,7 @@
       </c>
       <c r="H12" s="112" t="inlineStr">
         <is>
-          <t>Kira &amp; Sabit Gider</t>
+          <t>Genel Yönetim</t>
         </is>
       </c>
       <c r="I12" s="116" t="inlineStr">
@@ -32255,10 +32260,10 @@
       </c>
       <c r="D13" s="119" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="120" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="171" t="n">
         <v>520800</v>
       </c>
       <c r="F13" s="121" t="n">
@@ -32292,10 +32297,10 @@
       </c>
       <c r="D14" s="112" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="113" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="171" t="n">
         <v>1120000</v>
       </c>
       <c r="F14" s="114" t="n">
@@ -32329,10 +32334,10 @@
       </c>
       <c r="D15" s="119" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="120" t="n">
+          <t>Operasyonel çıkış tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="171" t="n">
         <v>890000</v>
       </c>
       <c r="F15" s="121" t="n">
@@ -32416,14 +32421,14 @@
     <row r="2">
       <c r="B2" s="128" t="inlineStr">
         <is>
-          <t>SITE APARTMAN YONETIM SISTEMI — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>SITE/APARTMAN YÖNETIM SISTEMI — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="129" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · Site yöneticisi, yönetim kurulu, kat malikleri temsilcisi, SMMM</t>
         </is>
       </c>
     </row>
@@ -32502,10 +32507,9 @@
       </c>
       <c r="C9" s="69" t="n"/>
       <c r="D9" s="69" t="n"/>
-      <c r="E9" s="136" t="inlineStr">
-        <is>
-          <t>₺4.280.000</t>
-        </is>
+      <c r="E9" s="172">
+        <f>PANO!B7*0.8*0.22</f>
+        <v/>
       </c>
       <c r="F9" s="69" t="n"/>
       <c r="H9" s="133" t="inlineStr">
@@ -32515,10 +32519,9 @@
       </c>
       <c r="I9" s="69" t="n"/>
       <c r="J9" s="69" t="n"/>
-      <c r="K9" s="136" t="inlineStr">
-        <is>
-          <t>₺12.450.000</t>
-        </is>
+      <c r="K9" s="172">
+        <f>PANO!H7</f>
+        <v/>
       </c>
       <c r="L9" s="69" t="n"/>
     </row>
@@ -32530,10 +32533,9 @@
       </c>
       <c r="C10" s="69" t="n"/>
       <c r="D10" s="69" t="n"/>
-      <c r="E10" s="137" t="inlineStr">
-        <is>
-          <t>₺1.850.000 (Yeterli)</t>
-        </is>
+      <c r="E10" s="173">
+        <f>PANO!E7*0.75</f>
+        <v/>
       </c>
       <c r="F10" s="69" t="n"/>
       <c r="H10" s="133" t="inlineStr">
@@ -32543,10 +32545,9 @@
       </c>
       <c r="I10" s="69" t="n"/>
       <c r="J10" s="69" t="n"/>
-      <c r="K10" s="137" t="inlineStr">
-        <is>
-          <t>₺8.240.000</t>
-        </is>
+      <c r="K10" s="173">
+        <f>PANO!H7*0.75</f>
+        <v/>
       </c>
       <c r="L10" s="69" t="n"/>
     </row>
@@ -32558,10 +32559,9 @@
       </c>
       <c r="C11" s="69" t="n"/>
       <c r="D11" s="69" t="n"/>
-      <c r="E11" s="137" t="inlineStr">
-        <is>
-          <t>1.28x (Eşik: 1.10x)</t>
-        </is>
+      <c r="E11" s="174">
+        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <v/>
       </c>
       <c r="F11" s="69" t="n"/>
       <c r="H11" s="133" t="inlineStr">

--- a/EXCELARSIV_PRODUCTS/site-apartman-yonetim-sistemi/SiteApartmanYonetimSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/site-apartman-yonetim-sistemi/SiteApartmanYonetimSistemi.xlsx
@@ -124,7 +124,7 @@
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="80">
+  <fonts count="82">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -584,8 +584,20 @@
       <color rgb="FFA32D2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -763,6 +775,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0E6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -1133,7 +1151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1541,6 +1559,30 @@
     </xf>
     <xf numFmtId="171" fontId="62" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4909,20 +4951,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="147.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="141" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="142" t="inlineStr">
         <is>
@@ -5187,6 +5246,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="145" t="inlineStr">
         <is>
@@ -5285,7 +5345,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5298,21 +5358,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="88" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>KAPAK — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Site/Apartman Yönetim Sistemi</t>
         </is>
@@ -5325,6 +5403,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -5367,6 +5446,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -5395,6 +5475,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
@@ -5411,13 +5492,14 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="7">
-    <mergeCell ref="A1:T1"/>
+  <mergeCells count="8">
     <mergeCell ref="A9:N9"/>
     <mergeCell ref="A8:N8"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A7:N7"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A11:N11"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A10:N10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5431,27 +5513,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22.5" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>HIZLI BASLANGIC — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>3 adımda başlayın</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -5488,6 +5588,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
@@ -5530,11 +5631,12 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B7:J7"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="B10">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -5561,22 +5663,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>GIRDI — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Site ve dönem parametreleri</t>
         </is>
@@ -5680,8 +5799,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B12">
     <cfRule type="cellIs" priority="1" operator="lessThanOrEqual" dxfId="0">
@@ -5735,35 +5855,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17.5" customWidth="1" min="2" max="2"/>
+    <col width="18.5" customWidth="1" min="3" max="3"/>
+    <col width="14.5" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14.5" customWidth="1" min="6" max="6"/>
+    <col width="16.5" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>PAYDASLAR — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+      <c r="J1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Malik / paydaş kartları — ID disiplini (bakiye türetilir)</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -7876,8 +8008,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <conditionalFormatting sqref="H6:H36">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
@@ -7907,35 +8040,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14.5" customWidth="1" min="4" max="4"/>
+    <col width="23.5" customWidth="1" min="5" max="5"/>
+    <col width="14.5" customWidth="1" min="6" max="6"/>
+    <col width="14.5" customWidth="1" min="7" max="7"/>
+    <col width="13.5" customWidth="1" min="8" max="8"/>
+    <col width="14.5" customWidth="1" min="9" max="9"/>
+    <col width="13.5" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>DONEMLER — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+      <c r="J1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Dönem borçlandırma motoru — aidat + gecikme zammı tabanı</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -10192,8 +10337,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <conditionalFormatting sqref="H6:H36">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
@@ -10224,33 +10370,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L86"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="23.5" customWidth="1" min="5" max="5"/>
+    <col width="14.5" customWidth="1" min="6" max="6"/>
+    <col width="16.5" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>TAHSILAT — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Ödeme girişi — eşleştirme motoruna besleme</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -11765,8 +11921,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="D6:D1005" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ödeme" error="0 veya üzeri" promptTitle="Ödeme" prompt="≥ 0" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
@@ -11792,35 +11949,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="3" max="3"/>
+    <col width="18.5" customWidth="1" min="4" max="4"/>
+    <col width="15.5" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="16.5" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>ANAHTAR — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+      <c r="J1" s="176" t="n"/>
+      <c r="K1" s="176" t="n"/>
+      <c r="L1" s="176" t="n"/>
+      <c r="M1" s="176" t="n"/>
+      <c r="N1" s="176" t="n"/>
+      <c r="O1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Normalize malik+dönem anahtarı + duplike (E01/E05)</t>
         </is>
@@ -16146,8 +16319,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A3:O3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="2">
@@ -16164,7 +16338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R86"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -16174,23 +16348,39 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="18.5" customWidth="1" min="8" max="8"/>
+    <col width="17.5" customWidth="1" min="9" max="9"/>
+    <col width="12.5" customWidth="1" min="10" max="10"/>
+    <col width="13.5" customWidth="1" min="11" max="11"/>
+    <col width="13.5" customWidth="1" min="12" max="12"/>
+    <col width="16.5" customWidth="1" min="13" max="13"/>
+    <col width="12.5" customWidth="1" min="14" max="14"/>
+    <col width="12.5" customWidth="1" min="15" max="15"/>
+    <col width="13.5" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>ESLESTIRME — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+      <c r="J1" s="176" t="n"/>
+      <c r="K1" s="176" t="n"/>
+      <c r="L1" s="176" t="n"/>
+      <c r="M1" s="176" t="n"/>
+      <c r="N1" s="176" t="n"/>
+      <c r="O1" s="176" t="n"/>
+      <c r="P1" s="176" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -16203,13 +16393,14 @@
         <v/>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Dört kova — borç↔tahsilat (E02/E03)</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -21640,8 +21831,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:R1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="C2">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -21673,7 +21865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -21681,22 +21873,35 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14.5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="17.5" customWidth="1" min="9" max="9"/>
+    <col width="16.5" customWidth="1" min="10" max="10"/>
+    <col width="47.5" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>KOK NEDEN — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+      <c r="J1" s="176" t="n"/>
+      <c r="K1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Kök neden — eşleşmeyen fark; TANIMSIZ elle incele (E04)</t>
         </is>
@@ -23954,8 +24159,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D46">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -23976,40 +24182,57 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T86"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16.5" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="23.5" customWidth="1" min="4" max="4"/>
+    <col width="23.5" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="6" max="6"/>
+    <col width="14.5" customWidth="1" min="7" max="7"/>
+    <col width="14.5" customWidth="1" min="8" max="8"/>
+    <col width="15.5" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="14.5" customWidth="1" min="11" max="11"/>
+    <col width="15.5" customWidth="1" min="12" max="12"/>
+    <col width="16.5" customWidth="1" min="13" max="13"/>
+    <col width="16.5" customWidth="1" min="14" max="14"/>
+    <col width="13.5" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>AKIS — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+      <c r="J1" s="176" t="n"/>
+      <c r="K1" s="176" t="n"/>
+      <c r="L1" s="176" t="n"/>
+      <c r="M1" s="176" t="n"/>
+      <c r="N1" s="176" t="n"/>
+      <c r="O1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>İcap durum makinesi — yetim / geçersiz geçiş / ZİNCİR KIRIK</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -26813,8 +27036,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:T1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A3:O3"/>
   </mergeCells>
   <conditionalFormatting sqref="L6:L56">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -26854,22 +27078,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="64.5" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="36.5" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="11.5" customWidth="1" min="7" max="7"/>
+    <col width="75.5" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15.5" customWidth="1" min="10" max="10"/>
+    <col width="81.5" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26903,6 +27128,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="68" t="inlineStr">
         <is>
@@ -27033,6 +27259,7 @@
       <c r="L9" s="69" t="n"/>
       <c r="M9" s="69" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="59" t="inlineStr">
         <is>
@@ -27062,6 +27289,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="85" t="inlineStr">
         <is>
@@ -27316,6 +27544,7 @@
         <v>92</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="96" t="inlineStr">
         <is>
@@ -27404,13 +27633,21 @@
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
+      <c r="G26" s="177" t="n"/>
+      <c r="H26" s="177" t="n"/>
+      <c r="I26" s="178" t="n"/>
       <c r="K26" s="105" t="inlineStr">
         <is>
           <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="F27" s="179" t="n"/>
+      <c r="G27" s="180" t="n"/>
+      <c r="H27" s="180" t="n"/>
+      <c r="I27" s="181" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K26:M27"/>
@@ -27428,33 +27665,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L86"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18.5" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15.5" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>GIDER — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Gider takibi — bütçe vs gerçekleşen</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -28843,8 +29090,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F36">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="4">
@@ -28874,31 +29122,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L86"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="23.5" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>KARARLAR — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Genel kurul / yönetim kararları — kanıt niteliğinde defter</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -29557,8 +29819,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="D6:D1005" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Liste" error="Listeden seçin" promptTitle="Sonuç" prompt="Listeden" type="list" errorStyle="stop">
@@ -29583,28 +29846,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18.5" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>KARAR — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Karar kapısı ve gerekçe</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
@@ -29627,6 +29907,7 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
@@ -29671,6 +29952,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
@@ -29815,9 +30097,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -29859,20 +30142,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="129.5" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>RAPOR — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
@@ -29881,8 +30179,8 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Ürün: Site/Apartman Yönetim Sistemi · Sürüm 1.0.0</t>
         </is>
@@ -29921,6 +30219,7 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
@@ -29994,6 +30293,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
@@ -30009,6 +30309,7 @@
       </c>
     </row>
     <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
@@ -30021,6 +30322,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
@@ -30033,6 +30335,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
@@ -30042,9 +30345,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:H18"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -30077,27 +30381,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="50.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>KONTROLLER — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Çalışma kitabı sağlık paneli</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
@@ -30188,8 +30510,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B12">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -30219,27 +30542,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="82.5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>ORNEK VERI — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Demo veri özeti — üretim örnekleri</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
@@ -30280,6 +30621,7 @@
         <v>18</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -30289,8 +30631,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30303,23 +30646,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14.5" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="19.5" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>LISTELER — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -30327,6 +30684,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -30457,7 +30815,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30470,31 +30828,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="23.5" customWidth="1" min="1" max="1"/>
+    <col width="23.5" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14.5" customWidth="1" min="5" max="5"/>
+    <col width="24.5" customWidth="1" min="6" max="6"/>
+    <col width="14.5" customWidth="1" min="7" max="7"/>
+    <col width="14.5" customWidth="1" min="8" max="8"/>
+    <col width="8.5" customWidth="1" min="9" max="9"/>
+    <col width="27.5" customWidth="1" min="10" max="10"/>
+    <col width="12.5" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>AYARLAR — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+      <c r="J1" s="176" t="n"/>
+      <c r="K1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Tek kaynak parametreler + durum haritası (A01/A06)</t>
         </is>
@@ -31785,8 +32157,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -31800,26 +32173,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="94.5" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>KILAVUZ — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>Kullanım kılavuzu</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
@@ -31885,14 +32277,15 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A6:H6"/>
@@ -31908,18 +32301,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="36.5" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="37.5" customWidth="1" min="4" max="4"/>
+    <col width="18.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22.5" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31929,12 +32323,16 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="106" t="inlineStr">
         <is>
           <t>🔍  SITE/APARTMAN YÖNETIM SISTEMI — Kayıt veya hesap ara...</t>
         </is>
       </c>
+      <c r="C3" s="182" t="n"/>
+      <c r="D3" s="182" t="n"/>
+      <c r="E3" s="183" t="n"/>
       <c r="G3" s="107" t="inlineStr">
         <is>
           <t>TOPLAM: 1.450 KAYIT</t>
@@ -31946,6 +32344,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="109" t="inlineStr">
         <is>
@@ -32358,22 +32757,17 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="126" t="inlineStr">
         <is>
           <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
         </is>
       </c>
-      <c r="C17" s="94" t="n"/>
-      <c r="D17" s="94" t="n"/>
       <c r="E17" s="127">
         <f>TOPLA(E6:E15)</f>
         <v/>
       </c>
-      <c r="F17" s="94" t="n"/>
-      <c r="G17" s="94" t="n"/>
-      <c r="H17" s="94" t="n"/>
-      <c r="I17" s="94" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -32394,7 +32788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -32439,25 +32833,26 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="131" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="69" t="n"/>
-      <c r="D6" s="69" t="n"/>
-      <c r="E6" s="69" t="n"/>
-      <c r="F6" s="69" t="n"/>
+      <c r="C6" s="182" t="n"/>
+      <c r="D6" s="182" t="n"/>
+      <c r="E6" s="182" t="n"/>
+      <c r="F6" s="183" t="n"/>
       <c r="H6" s="132" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="69" t="n"/>
-      <c r="J6" s="69" t="n"/>
-      <c r="K6" s="69" t="n"/>
-      <c r="L6" s="69" t="n"/>
+      <c r="I6" s="182" t="n"/>
+      <c r="J6" s="182" t="n"/>
+      <c r="K6" s="182" t="n"/>
+      <c r="L6" s="183" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="69" t="n"/>
@@ -32608,32 +33003,33 @@
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="69" t="n"/>
-      <c r="D14" s="69" t="n"/>
-      <c r="E14" s="69" t="n"/>
-      <c r="F14" s="69" t="n"/>
+      <c r="C14" s="184" t="n"/>
+      <c r="D14" s="184" t="n"/>
+      <c r="E14" s="184" t="n"/>
+      <c r="F14" s="185" t="n"/>
       <c r="H14" s="139" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="69" t="n"/>
-      <c r="J14" s="69" t="n"/>
-      <c r="K14" s="69" t="n"/>
-      <c r="L14" s="69" t="n"/>
+      <c r="I14" s="186" t="n"/>
+      <c r="J14" s="186" t="n"/>
+      <c r="K14" s="186" t="n"/>
+      <c r="L14" s="187" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="69" t="n"/>
-      <c r="C15" s="69" t="n"/>
-      <c r="D15" s="69" t="n"/>
-      <c r="E15" s="69" t="n"/>
-      <c r="F15" s="69" t="n"/>
-      <c r="H15" s="69" t="n"/>
-      <c r="I15" s="69" t="n"/>
-      <c r="J15" s="69" t="n"/>
-      <c r="K15" s="69" t="n"/>
-      <c r="L15" s="69" t="n"/>
-    </row>
+      <c r="B15" s="188" t="n"/>
+      <c r="C15" s="189" t="n"/>
+      <c r="D15" s="189" t="n"/>
+      <c r="E15" s="189" t="n"/>
+      <c r="F15" s="190" t="n"/>
+      <c r="H15" s="191" t="n"/>
+      <c r="I15" s="192" t="n"/>
+      <c r="J15" s="192" t="n"/>
+      <c r="K15" s="192" t="n"/>
+      <c r="L15" s="193" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="46" t="inlineStr">
         <is>
@@ -32641,6 +33037,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="96" t="inlineStr">
         <is>
@@ -32715,25 +33112,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30.5" customWidth="1" min="2" max="2"/>
+    <col width="23.5" customWidth="1" min="3" max="3"/>
+    <col width="48.5" customWidth="1" min="4" max="4"/>
+    <col width="43.5" customWidth="1" min="5" max="5"/>
+    <col width="21.5" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="146" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="147" t="inlineStr">
         <is>
@@ -33193,7 +33602,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33206,22 +33615,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="89.5" customWidth="1" min="2" max="2"/>
+    <col width="34.5" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="149" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="150" t="inlineStr">
         <is>
@@ -33933,7 +34357,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33946,24 +34370,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30.5" customWidth="1" min="1" max="1"/>
+    <col width="71.5" customWidth="1" min="2" max="2"/>
+    <col width="160.5" customWidth="1" min="3" max="3"/>
+    <col width="70.5" customWidth="1" min="4" max="4"/>
+    <col width="50.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="154" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="155" t="inlineStr">
         <is>
@@ -34606,7 +35043,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34619,24 +35056,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22.5" customWidth="1" min="1" max="1"/>
+    <col width="60.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="40.5" customWidth="1" min="4" max="4"/>
+    <col width="39.5" customWidth="1" min="5" max="5"/>
+    <col width="27.5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="158" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="159" t="inlineStr">
         <is>
@@ -35151,7 +35601,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35164,23 +35614,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20.5" customWidth="1" min="1" max="1"/>
+    <col width="41.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="35.5" customWidth="1" min="4" max="4"/>
+    <col width="33.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="161" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="175" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+      <c r="I1" s="176" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="162" t="inlineStr">
         <is>
@@ -35727,7 +36191,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/site-apartman-yonetim-sistemi/SiteApartmanYonetimSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/site-apartman-yonetim-sistemi/SiteApartmanYonetimSistemi.xlsx
@@ -4951,7 +4951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4972,14 +4972,6 @@
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -5358,7 +5350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="88" customWidth="1" min="1" max="1"/>
@@ -5379,14 +5371,6 @@
           <t>KAPAK — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -5513,7 +5497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -5534,14 +5518,6 @@
           <t>HIZLI BASLANGIC — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -5663,7 +5639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5684,14 +5660,6 @@
           <t>GIRDI — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -5855,7 +5823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -5877,15 +5845,6 @@
           <t>PAYDASLAR — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
-      <c r="J1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -8040,7 +7999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -8062,15 +8021,6 @@
           <t>DONEMLER — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
-      <c r="J1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -10370,7 +10320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -10390,13 +10340,6 @@
           <t>TAHSILAT — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -11949,7 +11892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -11976,20 +11919,6 @@
           <t>ANAHTAR — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
-      <c r="J1" s="176" t="n"/>
-      <c r="K1" s="176" t="n"/>
-      <c r="L1" s="176" t="n"/>
-      <c r="M1" s="176" t="n"/>
-      <c r="N1" s="176" t="n"/>
-      <c r="O1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -16338,7 +16267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -16366,21 +16295,6 @@
           <t>ESLESTIRME — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
-      <c r="J1" s="176" t="n"/>
-      <c r="K1" s="176" t="n"/>
-      <c r="L1" s="176" t="n"/>
-      <c r="M1" s="176" t="n"/>
-      <c r="N1" s="176" t="n"/>
-      <c r="O1" s="176" t="n"/>
-      <c r="P1" s="176" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -21865,7 +21779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -21888,16 +21802,6 @@
           <t>KOK NEDEN — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
-      <c r="J1" s="176" t="n"/>
-      <c r="K1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -24182,7 +24086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -24209,20 +24113,6 @@
           <t>AKIS — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
-      <c r="J1" s="176" t="n"/>
-      <c r="K1" s="176" t="n"/>
-      <c r="L1" s="176" t="n"/>
-      <c r="M1" s="176" t="n"/>
-      <c r="N1" s="176" t="n"/>
-      <c r="O1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -27078,7 +26968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -27209,7 +27099,7 @@
       <c r="I7" s="69" t="n"/>
       <c r="J7" s="69" t="n"/>
       <c r="K7" s="80">
-        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
       <c r="L7" s="69" t="n"/>
@@ -27514,11 +27404,11 @@
         </is>
       </c>
       <c r="I19" s="169">
-        <f>TOPLA(I15:I18)</f>
+        <f>SUM(I15:I18)</f>
         <v/>
       </c>
       <c r="J19" s="170">
-        <f>TOPLA(J15:J18)</f>
+        <f>SUM(J15:J18)</f>
         <v/>
       </c>
       <c r="K19" s="94" t="inlineStr"/>
@@ -27665,7 +27555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -27685,13 +27575,6 @@
           <t>GIDER — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -29122,7 +29005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -29143,14 +29026,6 @@
           <t>KARARLAR — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -29846,7 +29721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -29867,14 +29742,6 @@
           <t>KARAR — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -30142,7 +30009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="129.5" customWidth="1" min="1" max="1"/>
@@ -30163,14 +30030,6 @@
           <t>RAPOR — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
@@ -30381,7 +30240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -30402,14 +30261,6 @@
           <t>KONTROLLER — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -30542,7 +30393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="82.5" customWidth="1" min="1" max="1"/>
@@ -30563,14 +30414,6 @@
           <t>ORNEK VERI — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -30646,7 +30489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -30667,14 +30510,6 @@
           <t>LISTELER — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -30828,7 +30663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.5" customWidth="1" min="1" max="1"/>
@@ -30853,16 +30688,6 @@
           <t>AYARLAR — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
-      <c r="J1" s="176" t="n"/>
-      <c r="K1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -31682,7 +31507,7 @@
         </is>
       </c>
       <c r="N21" s="12">
-        <f>IF(say_kararKapi="VERİ YOK","Borç satırı yok — veri girin",IF(say_kararKapi="KRİTİK","Tahsilat oranı kritik veya ZİNCİR KIRIK var",IF(say_kararKapi="DİKKAT","Hedef altı tahsilat veya yetim/geçersiz geçiş","Tahsilat ve akış eşikleri içinde")))</f>
+        <f>IF(say_kararKapi="VERİ YOK","Borç satırı yok — veri girin",IF(say_kararKapi="KRİTİK","Tahsilat oranı kritik veya ZİNCİR KIRIK var",IF(say_kararKapi="DİKKAT","Hedef altı tahsilat veya yetim/geçersiz geçiş","Tahsilat AND akış eşikleri içinde")))</f>
         <v/>
       </c>
     </row>
@@ -32173,7 +31998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="94.5" customWidth="1" min="1" max="1"/>
@@ -32194,14 +32019,6 @@
           <t>KILAVUZ — Site/Apartman Yönetim Sistemi</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -32301,7 +32118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -32765,7 +32582,7 @@
         </is>
       </c>
       <c r="E17" s="127">
-        <f>TOPLA(E6:E15)</f>
+        <f>SUM(E6:E15)</f>
         <v/>
       </c>
     </row>
@@ -32788,7 +32605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -32955,7 +32772,7 @@
       <c r="C11" s="69" t="n"/>
       <c r="D11" s="69" t="n"/>
       <c r="E11" s="174">
-        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
       <c r="F11" s="69" t="n"/>
@@ -33112,7 +32929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -33133,14 +32950,6 @@
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -33615,7 +33424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -33636,14 +33445,6 @@
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -34370,7 +34171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.5" customWidth="1" min="1" max="1"/>
@@ -34391,14 +34192,6 @@
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -35056,7 +34849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -35077,14 +34870,6 @@
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -35614,7 +35399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" min="1" max="1"/>
@@ -35635,14 +35420,6 @@
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">

--- a/EXCELARSIV_PRODUCTS/site-apartman-yonetim-sistemi/SiteApartmanYonetimSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/site-apartman-yonetim-sistemi/SiteApartmanYonetimSistemi.xlsx
@@ -124,7 +124,7 @@
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="82">
+  <fonts count="117">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -596,8 +596,214 @@
       <color rgb="00475569"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00115E59"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F87171"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A7F3D0"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -783,8 +989,32 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+        <bgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="35">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1147,11 +1377,353 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="292">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1583,6 +2155,235 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="17" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="17" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="17" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="17" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="85" fillId="17" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="87" fillId="17" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="85" fillId="17" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="17" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="91" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="6" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="6" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="35" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="60" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="93" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="35" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="60" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="97" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="99" fillId="6" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="100" fillId="6" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="101" fillId="6" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="17" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="108" fillId="16" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="103" fillId="17" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="17" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="103" fillId="17" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="104" fillId="17" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="16" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="17" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="106" fillId="17" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="110" fillId="11" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="10" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="17" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="112" fillId="17" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="17" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="116" fillId="17" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="102" fillId="17" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="113" fillId="17" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="113" fillId="17" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="17" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="11" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="10" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="17" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="102" fillId="17" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="17" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4973,7 +5774,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="142" t="inlineStr">
         <is>
@@ -5238,7 +6038,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="145" t="inlineStr">
         <is>
@@ -5372,7 +6171,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -5387,7 +6185,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -5430,7 +6227,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -5459,7 +6255,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
@@ -5519,7 +6314,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -5527,7 +6321,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -5564,7 +6357,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
@@ -5661,7 +6453,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -5846,7 +6637,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -5854,7 +6644,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -8022,7 +8811,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -8030,7 +8818,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -10341,7 +11128,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -10349,7 +11135,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -11920,7 +12705,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -16314,7 +17098,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -21803,7 +22586,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -24114,7 +24896,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -24122,7 +24903,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -26971,554 +27751,585 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="64.5" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
-    <col width="36.5" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="11.5" customWidth="1" min="7" max="7"/>
-    <col width="75.5" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15.5" customWidth="1" min="10" max="10"/>
-    <col width="81.5" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="64" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="196" t="inlineStr">
         <is>
           <t>SITE/APARTMAN YÖNETIM SISTEMI</t>
         </is>
       </c>
-      <c r="L2" s="65" t="inlineStr">
+      <c r="L2" s="197" t="inlineStr">
         <is>
           <t>Dönem: 2026 / Tam ▼</t>
         </is>
       </c>
-      <c r="M2" s="66" t="inlineStr">
+      <c r="M2" s="198" t="inlineStr">
         <is>
           <t>★ DOĞRULANMIŞ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="67" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="199" t="inlineStr">
         <is>
           <t>Hedef Kullanıcı: Site yöneticisi, yönetim kurulu, kat malikleri temsilcisi, SMMM · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="B5" s="68" t="inlineStr">
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="200" t="inlineStr">
         <is>
           <t>TAHSILAT ORANI</t>
         </is>
       </c>
-      <c r="C5" s="69" t="n"/>
-      <c r="D5" s="70" t="inlineStr">
+      <c r="C5" s="201" t="n"/>
+      <c r="D5" s="202" t="inlineStr">
         <is>
           <t>KONSOLİDE</t>
         </is>
       </c>
-      <c r="E5" s="71" t="inlineStr">
+      <c r="E5" s="203" t="inlineStr">
         <is>
           <t>AIDAT TREND</t>
         </is>
       </c>
-      <c r="F5" s="69" t="n"/>
-      <c r="G5" s="72" t="inlineStr">
+      <c r="F5" s="201" t="n"/>
+      <c r="G5" s="204" t="inlineStr">
         <is>
           <t>KONTROL</t>
         </is>
       </c>
-      <c r="H5" s="68" t="inlineStr">
+      <c r="H5" s="205" t="inlineStr">
         <is>
           <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
-      <c r="I5" s="69" t="n"/>
-      <c r="J5" s="73" t="inlineStr">
+      <c r="I5" s="201" t="n"/>
+      <c r="J5" s="206" t="inlineStr">
         <is>
           <t>GÜVENLİ</t>
         </is>
       </c>
-      <c r="K5" s="74" t="inlineStr">
+      <c r="K5" s="207" t="inlineStr">
         <is>
           <t>SİSTEM GÜVEN SKORU</t>
         </is>
       </c>
-      <c r="L5" s="69" t="n"/>
-      <c r="M5" s="70" t="inlineStr">
+      <c r="L5" s="201" t="n"/>
+      <c r="M5" s="208" t="inlineStr">
         <is>
           <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="75" t="n"/>
-      <c r="C6" s="69" t="n"/>
-      <c r="D6" s="69" t="n"/>
-      <c r="E6" s="76" t="n"/>
-      <c r="F6" s="69" t="n"/>
-      <c r="G6" s="69" t="n"/>
-      <c r="H6" s="75" t="n"/>
-      <c r="I6" s="69" t="n"/>
-      <c r="J6" s="69" t="n"/>
-      <c r="K6" s="77" t="n"/>
-      <c r="L6" s="69" t="n"/>
-      <c r="M6" s="69" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="165">
+    <row r="6" ht="6" customHeight="1">
+      <c r="B6" s="209" t="n"/>
+      <c r="C6" s="210" t="n"/>
+      <c r="D6" s="211" t="n"/>
+      <c r="E6" s="212" t="n"/>
+      <c r="F6" s="210" t="n"/>
+      <c r="G6" s="211" t="n"/>
+      <c r="H6" s="213" t="n"/>
+      <c r="I6" s="210" t="n"/>
+      <c r="J6" s="211" t="n"/>
+      <c r="K6" s="214" t="n"/>
+      <c r="L6" s="210" t="n"/>
+      <c r="M6" s="211" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="215">
         <f>GİRDİLER!E17</f>
         <v/>
       </c>
-      <c r="C7" s="69" t="n"/>
-      <c r="D7" s="69" t="n"/>
-      <c r="E7" s="166">
+      <c r="C7" s="210" t="n"/>
+      <c r="D7" s="211" t="n"/>
+      <c r="E7" s="216">
         <f>B7*0.22</f>
         <v/>
       </c>
-      <c r="F7" s="69" t="n"/>
-      <c r="G7" s="69" t="n"/>
-      <c r="H7" s="165">
+      <c r="F7" s="210" t="n"/>
+      <c r="G7" s="211" t="n"/>
+      <c r="H7" s="217">
         <f>B7-E7</f>
         <v/>
       </c>
-      <c r="I7" s="69" t="n"/>
-      <c r="J7" s="69" t="n"/>
-      <c r="K7" s="80">
+      <c r="I7" s="210" t="n"/>
+      <c r="J7" s="211" t="n"/>
+      <c r="K7" s="218">
         <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
-      <c r="L7" s="69" t="n"/>
-      <c r="M7" s="69" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="75" t="n"/>
-      <c r="C8" s="69" t="n"/>
-      <c r="D8" s="69" t="n"/>
-      <c r="E8" s="76" t="n"/>
-      <c r="F8" s="69" t="n"/>
-      <c r="G8" s="69" t="n"/>
-      <c r="H8" s="75" t="n"/>
-      <c r="I8" s="69" t="n"/>
-      <c r="J8" s="69" t="n"/>
-      <c r="K8" s="77" t="n"/>
-      <c r="L8" s="69" t="n"/>
-      <c r="M8" s="69" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="81" t="inlineStr">
+      <c r="L7" s="210" t="n"/>
+      <c r="M7" s="211" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1">
+      <c r="B8" s="209" t="n"/>
+      <c r="C8" s="210" t="n"/>
+      <c r="D8" s="211" t="n"/>
+      <c r="E8" s="212" t="n"/>
+      <c r="F8" s="210" t="n"/>
+      <c r="G8" s="211" t="n"/>
+      <c r="H8" s="213" t="n"/>
+      <c r="I8" s="210" t="n"/>
+      <c r="J8" s="211" t="n"/>
+      <c r="K8" s="214" t="n"/>
+      <c r="L8" s="210" t="n"/>
+      <c r="M8" s="211" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="219" t="inlineStr">
         <is>
           <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
-      <c r="C9" s="69" t="n"/>
-      <c r="D9" s="69" t="n"/>
-      <c r="E9" s="82" t="inlineStr">
+      <c r="C9" s="220" t="n"/>
+      <c r="D9" s="221" t="n"/>
+      <c r="E9" s="222" t="inlineStr">
         <is>
           <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
-      <c r="F9" s="69" t="n"/>
-      <c r="G9" s="69" t="n"/>
-      <c r="H9" s="81" t="inlineStr">
+      <c r="F9" s="220" t="n"/>
+      <c r="G9" s="221" t="n"/>
+      <c r="H9" s="223" t="inlineStr">
         <is>
           <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
-      <c r="I9" s="69" t="n"/>
-      <c r="J9" s="69" t="n"/>
-      <c r="K9" s="83" t="inlineStr">
+      <c r="I9" s="220" t="n"/>
+      <c r="J9" s="221" t="n"/>
+      <c r="K9" s="224" t="inlineStr">
         <is>
           <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
-      <c r="L9" s="69" t="n"/>
-      <c r="M9" s="69" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="59" t="inlineStr">
+      <c r="L9" s="220" t="n"/>
+      <c r="M9" s="221" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="225" t="inlineStr">
         <is>
           <t>SITE/APARTMAN YÖNETIM SISTEMI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
-      <c r="F11" s="84" t="inlineStr">
+      <c r="F11" s="226" t="inlineStr">
         <is>
           <t>+%32 Verim</t>
         </is>
       </c>
-      <c r="H11" s="59" t="inlineStr">
+      <c r="H11" s="225" t="inlineStr">
         <is>
           <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="58" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="67" t="inlineStr">
         <is>
           <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
-      <c r="H12" s="58" t="inlineStr">
+      <c r="H12" s="67" t="inlineStr">
         <is>
           <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="85" t="inlineStr">
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="227" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C14" s="85" t="inlineStr">
+      <c r="C14" s="227" t="inlineStr">
         <is>
           <t>Aktif Hacim</t>
         </is>
       </c>
-      <c r="D14" s="85" t="inlineStr">
+      <c r="D14" s="227" t="inlineStr">
         <is>
           <t>Maliyet/Yük</t>
         </is>
       </c>
-      <c r="E14" s="85" t="inlineStr">
+      <c r="E14" s="227" t="inlineStr">
         <is>
           <t>Hedef</t>
         </is>
       </c>
-      <c r="H14" s="86" t="inlineStr">
+      <c r="H14" s="228" t="inlineStr">
         <is>
           <t>PARAMETRE / KALEM</t>
         </is>
       </c>
-      <c r="I14" s="86" t="inlineStr">
+      <c r="I14" s="229" t="inlineStr">
         <is>
           <t>ANA TUTAR</t>
         </is>
       </c>
-      <c r="J14" s="86" t="inlineStr">
+      <c r="J14" s="229" t="inlineStr">
         <is>
           <t>FARK / MARJ</t>
         </is>
       </c>
-      <c r="K14" s="86" t="inlineStr">
+      <c r="K14" s="229" t="inlineStr">
         <is>
           <t>VADE</t>
         </is>
       </c>
-      <c r="L14" s="86" t="inlineStr">
+      <c r="L14" s="229" t="inlineStr">
         <is>
           <t>KONTROL DURUMU</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="58" t="inlineStr">
+      <c r="M14" s="229" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="230" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C15" s="58" t="n">
+      <c r="C15" s="230" t="n">
         <v>65</v>
       </c>
-      <c r="D15" s="58" t="n">
+      <c r="D15" s="230" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="58" t="n">
+      <c r="E15" s="230" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="87" t="inlineStr">
+      <c r="H15" s="231" t="inlineStr">
         <is>
           <t>Dönemlik Kümülatif Bakiye</t>
         </is>
       </c>
-      <c r="I15" s="167">
+      <c r="I15" s="232">
         <f>B7*0.45</f>
         <v/>
       </c>
-      <c r="J15" s="168">
+      <c r="J15" s="233">
         <f>B7*0.05</f>
         <v/>
       </c>
-      <c r="K15" s="89" t="inlineStr">
+      <c r="K15" s="234" t="inlineStr">
         <is>
           <t>12 Ay</t>
         </is>
       </c>
-      <c r="L15" s="73" t="inlineStr">
+      <c r="L15" s="235" t="inlineStr">
         <is>
           <t>✓ DÜZENLİ</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="58" t="inlineStr">
+      <c r="M15" s="236" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="237" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C16" s="58" t="n">
+      <c r="C16" s="237" t="n">
         <v>78</v>
       </c>
-      <c r="D16" s="58" t="n">
+      <c r="D16" s="237" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="58" t="n">
+      <c r="E16" s="237" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="87" t="inlineStr">
+      <c r="H16" s="238" t="inlineStr">
         <is>
           <t>Kritik Eşik Güvenlik Tamponu</t>
         </is>
       </c>
-      <c r="I16" s="167">
+      <c r="I16" s="239">
         <f>B7*0.30</f>
         <v/>
       </c>
-      <c r="J16" s="168">
+      <c r="J16" s="240">
         <f>B7*0.03</f>
         <v/>
       </c>
-      <c r="K16" s="89" t="inlineStr">
+      <c r="K16" s="241" t="inlineStr">
         <is>
           <t>24 Ay</t>
         </is>
       </c>
-      <c r="L16" s="70" t="inlineStr">
+      <c r="L16" s="242" t="inlineStr">
         <is>
           <t>★ AVANTAJ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="58" t="inlineStr">
+      <c r="M16" s="243" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="230" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C17" s="58" t="n">
+      <c r="C17" s="230" t="n">
         <v>85</v>
       </c>
-      <c r="D17" s="58" t="n">
+      <c r="D17" s="230" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="58" t="n">
+      <c r="E17" s="230" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="87" t="inlineStr">
+      <c r="H17" s="231" t="inlineStr">
         <is>
           <t>Operasyonel Net Fark</t>
         </is>
       </c>
-      <c r="I17" s="167">
+      <c r="I17" s="232">
         <f>B7*0.15</f>
         <v/>
       </c>
-      <c r="J17" s="168">
+      <c r="J17" s="233">
         <f>B7*0.02</f>
         <v/>
       </c>
-      <c r="K17" s="89" t="inlineStr">
+      <c r="K17" s="234" t="inlineStr">
         <is>
           <t>8 Ay</t>
         </is>
       </c>
-      <c r="L17" s="90" t="inlineStr">
+      <c r="L17" s="244" t="inlineStr">
         <is>
           <t>● YAKLAŞAN</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="58" t="inlineStr">
+      <c r="M17" s="236" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="237" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C18" s="58" t="n">
+      <c r="C18" s="237" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="58" t="n">
+      <c r="D18" s="237" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="58" t="n">
+      <c r="E18" s="237" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="87" t="inlineStr">
+      <c r="H18" s="238" t="inlineStr">
         <is>
           <t>Rezerv ve Likit Dağılım</t>
         </is>
       </c>
-      <c r="I18" s="167">
+      <c r="I18" s="239">
         <f>B7*0.10</f>
         <v/>
       </c>
-      <c r="J18" s="168">
+      <c r="J18" s="240">
         <f>B7*0.01</f>
         <v/>
       </c>
-      <c r="K18" s="89" t="inlineStr">
+      <c r="K18" s="241" t="inlineStr">
         <is>
           <t>16 Ay</t>
         </is>
       </c>
-      <c r="L18" s="73" t="inlineStr">
+      <c r="L18" s="245" t="inlineStr">
         <is>
           <t>✓ TAM UYUM</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="58" t="inlineStr">
+      <c r="M18" s="243" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="230" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C19" s="58" t="n">
+      <c r="C19" s="230" t="n">
         <v>90</v>
       </c>
-      <c r="D19" s="58" t="n">
+      <c r="D19" s="230" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="58" t="n">
+      <c r="E19" s="230" t="n">
         <v>85</v>
       </c>
-      <c r="H19" s="91" t="inlineStr">
+      <c r="H19" s="246" t="inlineStr">
         <is>
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="169">
+      <c r="I19" s="247">
         <f>SUM(I15:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="170">
+      <c r="J19" s="248">
         <f>SUM(J15:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="94" t="inlineStr"/>
-      <c r="L19" s="95" t="inlineStr">
+      <c r="K19" s="249" t="inlineStr"/>
+      <c r="L19" s="250" t="inlineStr">
         <is>
           <t>TAM DOĞRULANDI (0 HATA)</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="58" t="inlineStr">
+      <c r="M19" s="250" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="237" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C20" s="58" t="n">
+      <c r="C20" s="237" t="n">
         <v>96</v>
       </c>
-      <c r="D20" s="58" t="n">
+      <c r="D20" s="237" t="n">
         <v>32</v>
       </c>
-      <c r="E20" s="58" t="n">
+      <c r="E20" s="237" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="96" t="inlineStr">
+    <row r="21" ht="14" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="251" t="inlineStr">
         <is>
           <t>KONSOLİDE PAY VE AĞIRLIK</t>
         </is>
       </c>
-      <c r="F22" s="96" t="inlineStr">
+      <c r="C22" s="201" t="n"/>
+      <c r="D22" s="201" t="n"/>
+      <c r="E22" s="252" t="n"/>
+      <c r="F22" s="251" t="inlineStr">
         <is>
           <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
         </is>
       </c>
-      <c r="K22" s="97" t="inlineStr">
+      <c r="G22" s="201" t="n"/>
+      <c r="H22" s="201" t="n"/>
+      <c r="I22" s="252" t="n"/>
+      <c r="K22" s="253" t="inlineStr">
         <is>
           <t>KARAR MOTORU</t>
         </is>
       </c>
-      <c r="L22" s="98" t="n"/>
-      <c r="M22" s="98" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="43" t="inlineStr">
+      <c r="L22" s="254" t="n"/>
+      <c r="M22" s="255" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="256" t="inlineStr">
         <is>
           <t>■ Ana Segment (%42)</t>
         </is>
       </c>
-      <c r="F23" s="58" t="inlineStr">
+      <c r="C23" s="210" t="n"/>
+      <c r="D23" s="210" t="n"/>
+      <c r="E23" s="211" t="n"/>
+      <c r="F23" s="257" t="inlineStr">
         <is>
           <t>Nakit Açığı Riski (30 Gün)</t>
         </is>
       </c>
-      <c r="I23" s="99" t="inlineStr">
+      <c r="G23" s="210" t="n"/>
+      <c r="H23" s="210" t="n"/>
+      <c r="I23" s="258" t="inlineStr">
         <is>
           <t>0.00 TL (Sıfır Risk)</t>
         </is>
       </c>
-      <c r="K23" s="100" t="inlineStr">
-        <is>
-          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
-        </is>
-      </c>
-      <c r="L23" s="98" t="n"/>
-      <c r="M23" s="98" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="44" t="inlineStr">
+      <c r="K23" s="259" t="inlineStr">
+        <is>
+          <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="260" t="n"/>
+      <c r="M23" s="261" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="262" t="inlineStr">
         <is>
           <t>■ İkincil Grup (%30)</t>
         </is>
       </c>
-      <c r="F24" s="58" t="inlineStr">
+      <c r="C24" s="210" t="n"/>
+      <c r="D24" s="210" t="n"/>
+      <c r="E24" s="211" t="n"/>
+      <c r="F24" s="257" t="inlineStr">
         <is>
           <t>Tahsilat Gecikme Toleransı</t>
         </is>
       </c>
-      <c r="I24" s="99" t="inlineStr">
+      <c r="G24" s="210" t="n"/>
+      <c r="H24" s="210" t="n"/>
+      <c r="I24" s="258" t="inlineStr">
         <is>
           <t>48 Gün Güvenli Eşik</t>
         </is>
       </c>
-      <c r="K24" s="101" t="inlineStr">
-        <is>
-          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="102" t="inlineStr">
+      <c r="K24" s="263" t="inlineStr">
+        <is>
+          <t>Atıl kalan nakit rezervinin gecelik repoda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="B25" s="264" t="inlineStr">
         <is>
           <t>■ Destek Birimi (%15)</t>
         </is>
       </c>
-      <c r="F25" s="43" t="inlineStr">
+      <c r="C25" s="210" t="n"/>
+      <c r="D25" s="210" t="n"/>
+      <c r="E25" s="211" t="n"/>
+      <c r="F25" s="235" t="inlineStr">
         <is>
           <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="103" t="inlineStr">
+      <c r="G25" s="265" t="n"/>
+      <c r="H25" s="265" t="n"/>
+      <c r="I25" s="265" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="266" t="inlineStr">
         <is>
           <t>■ Rezervler (%13)</t>
         </is>
       </c>
-      <c r="F26" s="104" t="inlineStr">
+      <c r="C26" s="210" t="n"/>
+      <c r="D26" s="210" t="n"/>
+      <c r="E26" s="211" t="n"/>
+      <c r="F26" s="267" t="inlineStr">
         <is>
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
@@ -27526,23 +28337,29 @@
       <c r="G26" s="177" t="n"/>
       <c r="H26" s="177" t="n"/>
       <c r="I26" s="178" t="n"/>
-      <c r="K26" s="105" t="inlineStr">
-        <is>
-          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+      <c r="K26" s="268" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE ›</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="269" t="n"/>
+      <c r="C27" s="220" t="n"/>
+      <c r="D27" s="220" t="n"/>
+      <c r="E27" s="221" t="n"/>
       <c r="F27" s="179" t="n"/>
       <c r="G27" s="180" t="n"/>
       <c r="H27" s="180" t="n"/>
       <c r="I27" s="181" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
+  <mergeCells count="5">
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27576,7 +28393,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -27584,7 +28400,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -29027,7 +29842,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -29035,7 +29849,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -29743,7 +30556,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -29751,7 +30563,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
@@ -29774,7 +30585,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
@@ -29819,7 +30629,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
@@ -30078,7 +30887,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
@@ -30152,7 +30960,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
@@ -30168,7 +30975,6 @@
       </c>
     </row>
     <row r="18"/>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
@@ -30181,7 +30987,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
@@ -30194,7 +30999,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
@@ -30262,7 +31066,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -30270,7 +31073,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
@@ -30415,7 +31217,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -30423,7 +31224,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
@@ -30464,7 +31264,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -30511,7 +31310,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -30519,7 +31317,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -30689,7 +31486,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -32020,7 +32816,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -32028,7 +32823,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
@@ -32140,7 +32934,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="106" t="inlineStr">
         <is>
@@ -32161,7 +32954,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="109" t="inlineStr">
         <is>
@@ -32574,7 +33366,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -32605,54 +33396,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="B2" s="128" t="inlineStr">
         <is>
           <t>SITE/APARTMAN YÖNETIM SISTEMI — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="129" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="270" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · Site yöneticisi, yönetim kurulu, kat malikleri temsilcisi, SMMM</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="130" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="271" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="131" t="inlineStr">
+    <row r="5" ht="12" customHeight="1"/>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="272" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
@@ -32661,7 +33453,7 @@
       <c r="D6" s="182" t="n"/>
       <c r="E6" s="182" t="n"/>
       <c r="F6" s="183" t="n"/>
-      <c r="H6" s="132" t="inlineStr">
+      <c r="H6" s="273" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
@@ -32671,151 +33463,151 @@
       <c r="K6" s="182" t="n"/>
       <c r="L6" s="183" t="n"/>
     </row>
-    <row r="7">
-      <c r="B7" s="69" t="n"/>
-      <c r="C7" s="69" t="n"/>
-      <c r="D7" s="69" t="n"/>
-      <c r="E7" s="69" t="n"/>
-      <c r="F7" s="69" t="n"/>
-      <c r="H7" s="69" t="n"/>
-      <c r="I7" s="69" t="n"/>
-      <c r="J7" s="69" t="n"/>
-      <c r="K7" s="69" t="n"/>
-      <c r="L7" s="69" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="133" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="274" t="n"/>
+      <c r="C7" s="210" t="n"/>
+      <c r="D7" s="210" t="n"/>
+      <c r="E7" s="210" t="n"/>
+      <c r="F7" s="275" t="n"/>
+      <c r="H7" s="276" t="n"/>
+      <c r="I7" s="210" t="n"/>
+      <c r="J7" s="210" t="n"/>
+      <c r="K7" s="210" t="n"/>
+      <c r="L7" s="277" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="278" t="inlineStr">
         <is>
           <t>Ciro / Hacim Düşüşü:</t>
         </is>
       </c>
-      <c r="C8" s="69" t="n"/>
-      <c r="D8" s="69" t="n"/>
-      <c r="E8" s="134" t="inlineStr">
+      <c r="C8" s="210" t="n"/>
+      <c r="D8" s="210" t="n"/>
+      <c r="E8" s="279" t="inlineStr">
         <is>
           <t>-%20.0 (Kriz Eşiği)</t>
         </is>
       </c>
-      <c r="F8" s="69" t="n"/>
-      <c r="H8" s="133" t="inlineStr">
+      <c r="F8" s="275" t="n"/>
+      <c r="H8" s="280" t="inlineStr">
         <is>
           <t>Ciro / Hacim Gerçekleşmesi:</t>
         </is>
       </c>
-      <c r="I8" s="69" t="n"/>
-      <c r="J8" s="69" t="n"/>
-      <c r="K8" s="135" t="inlineStr">
+      <c r="I8" s="210" t="n"/>
+      <c r="J8" s="210" t="n"/>
+      <c r="K8" s="281" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="69" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="133" t="inlineStr">
+      <c r="L8" s="277" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="278" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="C9" s="69" t="n"/>
-      <c r="D9" s="69" t="n"/>
-      <c r="E9" s="172">
+      <c r="C9" s="210" t="n"/>
+      <c r="D9" s="210" t="n"/>
+      <c r="E9" s="282">
         <f>PANO!B7*0.8*0.22</f>
         <v/>
       </c>
-      <c r="F9" s="69" t="n"/>
-      <c r="H9" s="133" t="inlineStr">
+      <c r="F9" s="275" t="n"/>
+      <c r="H9" s="280" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="I9" s="69" t="n"/>
-      <c r="J9" s="69" t="n"/>
-      <c r="K9" s="172">
+      <c r="I9" s="210" t="n"/>
+      <c r="J9" s="210" t="n"/>
+      <c r="K9" s="282">
         <f>PANO!H7</f>
         <v/>
       </c>
-      <c r="L9" s="69" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="133" t="inlineStr">
+      <c r="L9" s="277" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="278" t="inlineStr">
         <is>
           <t>Minimum Nakit Tamponu:</t>
         </is>
       </c>
-      <c r="C10" s="69" t="n"/>
-      <c r="D10" s="69" t="n"/>
-      <c r="E10" s="173">
+      <c r="C10" s="210" t="n"/>
+      <c r="D10" s="210" t="n"/>
+      <c r="E10" s="283">
         <f>PANO!E7*0.75</f>
         <v/>
       </c>
-      <c r="F10" s="69" t="n"/>
-      <c r="H10" s="133" t="inlineStr">
+      <c r="F10" s="275" t="n"/>
+      <c r="H10" s="280" t="inlineStr">
         <is>
           <t>Serbest Nakit Akımı:</t>
         </is>
       </c>
-      <c r="I10" s="69" t="n"/>
-      <c r="J10" s="69" t="n"/>
-      <c r="K10" s="173">
+      <c r="I10" s="210" t="n"/>
+      <c r="J10" s="210" t="n"/>
+      <c r="K10" s="283">
         <f>PANO!H7*0.75</f>
         <v/>
       </c>
-      <c r="L10" s="69" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="133" t="inlineStr">
+      <c r="L10" s="277" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="278" t="inlineStr">
         <is>
           <t>Likidite Karşılama Oranı:</t>
         </is>
       </c>
-      <c r="C11" s="69" t="n"/>
-      <c r="D11" s="69" t="n"/>
-      <c r="E11" s="174">
+      <c r="C11" s="210" t="n"/>
+      <c r="D11" s="210" t="n"/>
+      <c r="E11" s="284">
         <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
-      <c r="F11" s="69" t="n"/>
-      <c r="H11" s="133" t="inlineStr">
+      <c r="F11" s="275" t="n"/>
+      <c r="H11" s="280" t="inlineStr">
         <is>
           <t>Yatırım Geri Dönüşü (ROI):</t>
         </is>
       </c>
-      <c r="I11" s="69" t="n"/>
-      <c r="J11" s="69" t="n"/>
-      <c r="K11" s="137" t="inlineStr">
+      <c r="I11" s="210" t="n"/>
+      <c r="J11" s="210" t="n"/>
+      <c r="K11" s="285" t="inlineStr">
         <is>
           <t>%38.4 Yıllık</t>
         </is>
       </c>
-      <c r="L11" s="69" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="69" t="n"/>
-      <c r="C12" s="69" t="n"/>
-      <c r="D12" s="69" t="n"/>
-      <c r="E12" s="69" t="n"/>
-      <c r="F12" s="69" t="n"/>
-      <c r="H12" s="69" t="n"/>
-      <c r="I12" s="69" t="n"/>
-      <c r="J12" s="69" t="n"/>
-      <c r="K12" s="69" t="n"/>
-      <c r="L12" s="69" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="69" t="n"/>
-      <c r="C13" s="69" t="n"/>
-      <c r="D13" s="69" t="n"/>
-      <c r="E13" s="69" t="n"/>
-      <c r="F13" s="69" t="n"/>
-      <c r="H13" s="69" t="n"/>
-      <c r="I13" s="69" t="n"/>
-      <c r="J13" s="69" t="n"/>
-      <c r="K13" s="69" t="n"/>
-      <c r="L13" s="69" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="138" t="inlineStr">
+      <c r="L11" s="277" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="274" t="n"/>
+      <c r="C12" s="210" t="n"/>
+      <c r="D12" s="210" t="n"/>
+      <c r="E12" s="210" t="n"/>
+      <c r="F12" s="275" t="n"/>
+      <c r="H12" s="276" t="n"/>
+      <c r="I12" s="210" t="n"/>
+      <c r="J12" s="210" t="n"/>
+      <c r="K12" s="210" t="n"/>
+      <c r="L12" s="277" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="274" t="n"/>
+      <c r="C13" s="210" t="n"/>
+      <c r="D13" s="210" t="n"/>
+      <c r="E13" s="210" t="n"/>
+      <c r="F13" s="275" t="n"/>
+      <c r="H13" s="276" t="n"/>
+      <c r="I13" s="210" t="n"/>
+      <c r="J13" s="210" t="n"/>
+      <c r="K13" s="210" t="n"/>
+      <c r="L13" s="277" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="286" t="inlineStr">
         <is>
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
@@ -32824,7 +33616,7 @@
       <c r="D14" s="184" t="n"/>
       <c r="E14" s="184" t="n"/>
       <c r="F14" s="185" t="n"/>
-      <c r="H14" s="139" t="inlineStr">
+      <c r="H14" s="287" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
@@ -32834,7 +33626,7 @@
       <c r="K14" s="186" t="n"/>
       <c r="L14" s="187" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="188" t="n"/>
       <c r="C15" s="189" t="n"/>
       <c r="D15" s="189" t="n"/>
@@ -32846,70 +33638,185 @@
       <c r="K15" s="192" t="n"/>
       <c r="L15" s="193" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="46" t="inlineStr">
+    <row r="16" ht="10" customHeight="1"/>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="288" t="inlineStr">
         <is>
           <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="96" t="inlineStr">
+      <c r="C17" s="201" t="n"/>
+      <c r="D17" s="201" t="n"/>
+      <c r="E17" s="201" t="n"/>
+      <c r="F17" s="201" t="n"/>
+      <c r="G17" s="201" t="n"/>
+      <c r="H17" s="201" t="n"/>
+      <c r="I17" s="201" t="n"/>
+      <c r="J17" s="201" t="n"/>
+      <c r="K17" s="201" t="n"/>
+      <c r="L17" s="252" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="289" t="n"/>
+      <c r="C18" s="210" t="n"/>
+      <c r="D18" s="210" t="n"/>
+      <c r="E18" s="210" t="n"/>
+      <c r="F18" s="210" t="n"/>
+      <c r="G18" s="210" t="n"/>
+      <c r="H18" s="210" t="n"/>
+      <c r="I18" s="210" t="n"/>
+      <c r="J18" s="210" t="n"/>
+      <c r="K18" s="210" t="n"/>
+      <c r="L18" s="211" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="290" t="inlineStr">
         <is>
           <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="140" t="inlineStr">
+      <c r="C19" s="210" t="n"/>
+      <c r="D19" s="210" t="n"/>
+      <c r="E19" s="210" t="n"/>
+      <c r="F19" s="210" t="n"/>
+      <c r="G19" s="210" t="n"/>
+      <c r="H19" s="210" t="n"/>
+      <c r="I19" s="210" t="n"/>
+      <c r="J19" s="210" t="n"/>
+      <c r="K19" s="210" t="n"/>
+      <c r="L19" s="211" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="291" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="96" t="inlineStr">
+      <c r="C20" s="210" t="n"/>
+      <c r="D20" s="210" t="n"/>
+      <c r="E20" s="210" t="n"/>
+      <c r="F20" s="210" t="n"/>
+      <c r="G20" s="210" t="n"/>
+      <c r="H20" s="210" t="n"/>
+      <c r="I20" s="210" t="n"/>
+      <c r="J20" s="210" t="n"/>
+      <c r="K20" s="210" t="n"/>
+      <c r="L20" s="211" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="290" t="inlineStr">
         <is>
           <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="140" t="inlineStr">
+      <c r="C21" s="210" t="n"/>
+      <c r="D21" s="210" t="n"/>
+      <c r="E21" s="210" t="n"/>
+      <c r="F21" s="210" t="n"/>
+      <c r="G21" s="210" t="n"/>
+      <c r="H21" s="210" t="n"/>
+      <c r="I21" s="210" t="n"/>
+      <c r="J21" s="210" t="n"/>
+      <c r="K21" s="210" t="n"/>
+      <c r="L21" s="211" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="291" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="96" t="inlineStr">
+      <c r="C22" s="210" t="n"/>
+      <c r="D22" s="210" t="n"/>
+      <c r="E22" s="210" t="n"/>
+      <c r="F22" s="210" t="n"/>
+      <c r="G22" s="210" t="n"/>
+      <c r="H22" s="210" t="n"/>
+      <c r="I22" s="210" t="n"/>
+      <c r="J22" s="210" t="n"/>
+      <c r="K22" s="210" t="n"/>
+      <c r="L22" s="211" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="290" t="inlineStr">
         <is>
           <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="140" t="inlineStr">
+      <c r="C23" s="210" t="n"/>
+      <c r="D23" s="210" t="n"/>
+      <c r="E23" s="210" t="n"/>
+      <c r="F23" s="210" t="n"/>
+      <c r="G23" s="210" t="n"/>
+      <c r="H23" s="210" t="n"/>
+      <c r="I23" s="210" t="n"/>
+      <c r="J23" s="210" t="n"/>
+      <c r="K23" s="210" t="n"/>
+      <c r="L23" s="211" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="291" t="inlineStr">
         <is>
           <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="96" t="inlineStr">
+      <c r="C24" s="210" t="n"/>
+      <c r="D24" s="210" t="n"/>
+      <c r="E24" s="210" t="n"/>
+      <c r="F24" s="210" t="n"/>
+      <c r="G24" s="210" t="n"/>
+      <c r="H24" s="210" t="n"/>
+      <c r="I24" s="210" t="n"/>
+      <c r="J24" s="210" t="n"/>
+      <c r="K24" s="210" t="n"/>
+      <c r="L24" s="211" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="290" t="inlineStr">
         <is>
           <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="140" t="inlineStr">
+      <c r="C25" s="210" t="n"/>
+      <c r="D25" s="210" t="n"/>
+      <c r="E25" s="210" t="n"/>
+      <c r="F25" s="210" t="n"/>
+      <c r="G25" s="210" t="n"/>
+      <c r="H25" s="210" t="n"/>
+      <c r="I25" s="210" t="n"/>
+      <c r="J25" s="210" t="n"/>
+      <c r="K25" s="210" t="n"/>
+      <c r="L25" s="211" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="291" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
+      <c r="C26" s="210" t="n"/>
+      <c r="D26" s="210" t="n"/>
+      <c r="E26" s="210" t="n"/>
+      <c r="F26" s="210" t="n"/>
+      <c r="G26" s="210" t="n"/>
+      <c r="H26" s="210" t="n"/>
+      <c r="I26" s="210" t="n"/>
+      <c r="J26" s="210" t="n"/>
+      <c r="K26" s="210" t="n"/>
+      <c r="L26" s="211" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="269" t="n"/>
+      <c r="C27" s="220" t="n"/>
+      <c r="D27" s="220" t="n"/>
+      <c r="E27" s="220" t="n"/>
+      <c r="F27" s="220" t="n"/>
+      <c r="G27" s="220" t="n"/>
+      <c r="H27" s="220" t="n"/>
+      <c r="I27" s="220" t="n"/>
+      <c r="J27" s="220" t="n"/>
+      <c r="K27" s="220" t="n"/>
+      <c r="L27" s="221" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -32951,7 +33858,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="147" t="inlineStr">
         <is>
@@ -33446,7 +34352,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="150" t="inlineStr">
         <is>
@@ -34193,7 +35098,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="155" t="inlineStr">
         <is>
@@ -34871,7 +35775,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="159" t="inlineStr">
         <is>
@@ -35421,7 +36324,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="162" t="inlineStr">
         <is>
